--- a/R_Codes/DataSummary/Bacteria/Sample_Layer/Bacteria_Summary_Phylum_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_Layer/Bacteria_Summary_Phylum_by_Sample_Layer.xlsx
@@ -1076,10 +1076,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>28.7479203042606</v>
+        <v>28.7478386553316</v>
       </c>
       <c r="D2" t="n">
-        <v>0.98180823437789</v>
+        <v>0.981848803554123</v>
       </c>
     </row>
     <row r="3">
@@ -1090,10 +1090,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>21.2563038645289</v>
+        <v>21.2553954313553</v>
       </c>
       <c r="D3" t="n">
-        <v>0.248064707862375</v>
+        <v>0.248604830302399</v>
       </c>
     </row>
     <row r="4">
@@ -1104,10 +1104,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>8.12680157447302</v>
+        <v>8.12642412172715</v>
       </c>
       <c r="D4" t="n">
-        <v>0.235698134845426</v>
+        <v>0.235680686586157</v>
       </c>
     </row>
     <row r="5">
@@ -1118,10 +1118,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>6.95161865687162</v>
+        <v>6.95239373406009</v>
       </c>
       <c r="D5" t="n">
-        <v>0.241420895553324</v>
+        <v>0.241470268707046</v>
       </c>
     </row>
     <row r="6">
@@ -1132,10 +1132,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>5.87058410342007</v>
+        <v>5.87167930240257</v>
       </c>
       <c r="D6" t="n">
-        <v>2.11452278575145</v>
+        <v>2.11491571353179</v>
       </c>
     </row>
     <row r="7">
@@ -1146,10 +1146,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.65113431715435</v>
+        <v>4.64995465934387</v>
       </c>
       <c r="D7" t="n">
-        <v>0.114192182749829</v>
+        <v>0.114157895097351</v>
       </c>
     </row>
     <row r="8">
@@ -1160,10 +1160,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>4.12840069612117</v>
+        <v>4.12914189295195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.447746289989224</v>
+        <v>0.447822923197302</v>
       </c>
     </row>
     <row r="9">
@@ -1174,10 +1174,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>3.89846170733154</v>
+        <v>3.89867267556358</v>
       </c>
       <c r="D9" t="n">
-        <v>0.120260688576673</v>
+        <v>0.120268302843823</v>
       </c>
     </row>
     <row r="10">
@@ -1188,10 +1188,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>2.12921330731926</v>
+        <v>2.12936311171495</v>
       </c>
       <c r="D10" t="n">
-        <v>0.279659582605675</v>
+        <v>0.279696795724697</v>
       </c>
     </row>
     <row r="11">
@@ -1202,10 +1202,10 @@
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>2.09269450502849</v>
+        <v>2.09236811276501</v>
       </c>
       <c r="D11" t="n">
-        <v>0.248382899093778</v>
+        <v>0.248340631929808</v>
       </c>
     </row>
     <row r="12">
@@ -1216,10 +1216,10 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6922470409226</v>
+        <v>1.69270004170606</v>
       </c>
       <c r="D12" t="n">
-        <v>0.173340610285345</v>
+        <v>0.173378565526006</v>
       </c>
     </row>
     <row r="13">
@@ -1230,10 +1230,10 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>1.43352426584171</v>
+        <v>1.43354798253351</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0367325189116974</v>
+        <v>0.0367392143514061</v>
       </c>
     </row>
     <row r="14">
@@ -1244,10 +1244,10 @@
         <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>1.42734847293777</v>
+        <v>1.42718861013309</v>
       </c>
       <c r="D14" t="n">
-        <v>0.146706425832712</v>
+        <v>0.146714798419758</v>
       </c>
     </row>
     <row r="15">
@@ -1258,10 +1258,10 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>1.30910526256095</v>
+        <v>1.30901266941379</v>
       </c>
       <c r="D15" t="n">
-        <v>0.121574414509404</v>
+        <v>0.121597864776478</v>
       </c>
     </row>
     <row r="16">
@@ -1272,10 +1272,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>1.17340747353633</v>
+        <v>1.17350031644185</v>
       </c>
       <c r="D16" t="n">
-        <v>0.338602093967202</v>
+        <v>0.338630809103894</v>
       </c>
     </row>
     <row r="17">
@@ -1286,10 +1286,10 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>0.958808309604982</v>
+        <v>0.958666421434614</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0288634239375355</v>
+        <v>0.0288630076034351</v>
       </c>
     </row>
     <row r="18">
@@ -1300,10 +1300,10 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>0.548089904548614</v>
+        <v>0.548202744298505</v>
       </c>
       <c r="D18" t="n">
-        <v>0.11154636178912</v>
+        <v>0.111574248687405</v>
       </c>
     </row>
     <row r="19">
@@ -1314,10 +1314,10 @@
         <v>46</v>
       </c>
       <c r="C19" t="n">
-        <v>0.474080047102832</v>
+        <v>0.474078449829828</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0334656055947645</v>
+        <v>0.0334754521383822</v>
       </c>
     </row>
     <row r="20">
@@ -1328,10 +1328,10 @@
         <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>0.384863241334206</v>
+        <v>0.384898413094824</v>
       </c>
       <c r="D20" t="n">
-        <v>0.012924546975954</v>
+        <v>0.0129254988632066</v>
       </c>
     </row>
     <row r="21">
@@ -1342,10 +1342,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>0.355081991228914</v>
+        <v>0.355110663337299</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0180083008976812</v>
+        <v>0.0180122520605538</v>
       </c>
     </row>
     <row r="22">
@@ -1356,10 +1356,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>0.328802986950621</v>
+        <v>0.328783199564465</v>
       </c>
       <c r="D22" t="n">
-        <v>0.160279689859185</v>
+        <v>0.160259323900976</v>
       </c>
     </row>
     <row r="23">
@@ -1370,10 +1370,10 @@
         <v>48</v>
       </c>
       <c r="C23" t="n">
-        <v>0.284200960953612</v>
+        <v>0.28417687587404</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0669441643210855</v>
+        <v>0.066987001612437</v>
       </c>
     </row>
     <row r="24">
@@ -1384,10 +1384,10 @@
         <v>18</v>
       </c>
       <c r="C24" t="n">
-        <v>0.209941070205649</v>
+        <v>0.209900200751137</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0233829591327431</v>
+        <v>0.0233755660651689</v>
       </c>
     </row>
     <row r="25">
@@ -1398,10 +1398,10 @@
         <v>66</v>
       </c>
       <c r="C25" t="n">
-        <v>0.197837441504071</v>
+        <v>0.197746213044283</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0336309008506687</v>
+        <v>0.0336148153800416</v>
       </c>
     </row>
     <row r="26">
@@ -1412,10 +1412,10 @@
         <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>0.17988427924896</v>
+        <v>0.179816583497662</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0723896527640966</v>
+        <v>0.0723571392803332</v>
       </c>
     </row>
     <row r="27">
@@ -1426,10 +1426,10 @@
         <v>40</v>
       </c>
       <c r="C27" t="n">
-        <v>0.16840617870195</v>
+        <v>0.16835453440358</v>
       </c>
       <c r="D27" t="n">
-        <v>0.030880956965236</v>
+        <v>0.0308554736801004</v>
       </c>
     </row>
     <row r="28">
@@ -1440,10 +1440,10 @@
         <v>33</v>
       </c>
       <c r="C28" t="n">
-        <v>0.158863982500539</v>
+        <v>0.158827185989424</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0201618327566743</v>
+        <v>0.0201548226402213</v>
       </c>
     </row>
     <row r="29">
@@ -1454,10 +1454,10 @@
         <v>44</v>
       </c>
       <c r="C29" t="n">
-        <v>0.138735560176389</v>
+        <v>0.138714718394029</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0194640560503557</v>
+        <v>0.019461820852411</v>
       </c>
     </row>
     <row r="30">
@@ -1468,10 +1468,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.105474605799216</v>
+        <v>0.105486545499737</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00742901456022476</v>
+        <v>0.00743166924163284</v>
       </c>
     </row>
     <row r="31">
@@ -1482,10 +1482,10 @@
         <v>53</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0930675559017514</v>
+        <v>0.0930343186135997</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0280625254733637</v>
+        <v>0.0280504363780166</v>
       </c>
     </row>
     <row r="32">
@@ -1496,10 +1496,10 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0809161746952486</v>
+        <v>0.0809253928900969</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00574852847991997</v>
+        <v>0.00575125613111542</v>
       </c>
     </row>
     <row r="33">
@@ -1510,10 +1510,10 @@
         <v>38</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0740116370422383</v>
+        <v>0.0739811040873712</v>
       </c>
       <c r="D33" t="n">
-        <v>0.016662601831867</v>
+        <v>0.0166543471580114</v>
       </c>
     </row>
     <row r="34">
@@ -1524,7 +1524,7 @@
         <v>23</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0493805390829515</v>
+        <v>0.049385562069384</v>
       </c>
       <c r="D34"/>
     </row>
@@ -1536,10 +1536,10 @@
         <v>42</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0440426395107522</v>
+        <v>0.0440279294172811</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0077180442104827</v>
+        <v>0.00771516795991598</v>
       </c>
     </row>
     <row r="36">
@@ -1550,10 +1550,10 @@
         <v>56</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0387204597072548</v>
+        <v>0.0387023144901908</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0237289835700205</v>
+        <v>0.0237178636721463</v>
       </c>
     </row>
     <row r="37">
@@ -1564,10 +1564,10 @@
         <v>41</v>
       </c>
       <c r="C37" t="n">
-        <v>0.038075059392252</v>
+        <v>0.0380572166232709</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0187093666924253</v>
+        <v>0.0187005990919802</v>
       </c>
     </row>
     <row r="38">
@@ -1578,10 +1578,10 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0341166436734894</v>
+        <v>0.0341202222883923</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00975743339078427</v>
+        <v>0.00976077269909994</v>
       </c>
     </row>
     <row r="39">
@@ -1592,10 +1592,10 @@
         <v>36</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0322605245690374</v>
+        <v>0.0322676411439152</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00732265845560888</v>
+        <v>0.0073260396459104</v>
       </c>
     </row>
     <row r="40">
@@ -1606,10 +1606,10 @@
         <v>32</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0292147452332084</v>
+        <v>0.0292241785052206</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00702245913388988</v>
+        <v>0.00702534221622951</v>
       </c>
     </row>
     <row r="41">
@@ -1620,10 +1620,10 @@
         <v>43</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0263576031218012</v>
+        <v>0.0263473266207581</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0151305774219614</v>
+        <v>0.0151220195128035</v>
       </c>
     </row>
     <row r="42">
@@ -1634,10 +1634,10 @@
         <v>39</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0219999645978944</v>
+        <v>0.0219970664648839</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00916760645748471</v>
+        <v>0.00916855105468051</v>
       </c>
     </row>
     <row r="43">
@@ -1648,10 +1648,10 @@
         <v>62</v>
       </c>
       <c r="C43" t="n">
-        <v>0.017279584996208</v>
+        <v>0.017283049377617</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00301395593315887</v>
+        <v>0.00301609119242088</v>
       </c>
     </row>
     <row r="44">
@@ -1662,7 +1662,7 @@
         <v>50</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0122614195874155</v>
+        <v>0.0122556736298104</v>
       </c>
       <c r="D44"/>
     </row>
@@ -1674,10 +1674,10 @@
         <v>60</v>
       </c>
       <c r="C45" t="n">
-        <v>0.00838961089621756</v>
+        <v>0.00838567934912474</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00162408434469127</v>
+        <v>0.00162332326480773</v>
       </c>
     </row>
     <row r="46">
@@ -1688,7 +1688,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00774421058121475</v>
+        <v>0.00774058148220488</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>30</v>
       </c>
       <c r="C47" t="n">
-        <v>0.00451750560561018</v>
+        <v>0.00451538860802231</v>
       </c>
       <c r="D47"/>
     </row>
@@ -1714,7 +1714,7 @@
         <v>52</v>
       </c>
       <c r="C48" t="n">
-        <v>0.00322670497560457</v>
+        <v>0.00322519287418257</v>
       </c>
       <c r="D48"/>
     </row>
@@ -1726,7 +1726,7 @@
         <v>55</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00258130466060176</v>
+        <v>0.0025800950072627</v>
       </c>
       <c r="D49"/>
     </row>
@@ -1763,10 +1763,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>34.4514811528101</v>
+        <v>34.4531195146272</v>
       </c>
       <c r="D2" t="n">
-        <v>0.62143230851305</v>
+        <v>0.62142470246616</v>
       </c>
     </row>
     <row r="3">
@@ -1777,10 +1777,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>14.7563801304578</v>
+        <v>14.7562408978378</v>
       </c>
       <c r="D3" t="n">
-        <v>0.534601870579975</v>
+        <v>0.534560159005088</v>
       </c>
     </row>
     <row r="4">
@@ -1791,10 +1791,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>13.4267249451126</v>
+        <v>13.4263795865191</v>
       </c>
       <c r="D4" t="n">
-        <v>0.359382807907805</v>
+        <v>0.359320401529959</v>
       </c>
     </row>
     <row r="5">
@@ -1805,10 +1805,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>7.13014488841802</v>
+        <v>7.13080956462255</v>
       </c>
       <c r="D5" t="n">
-        <v>0.449011791897915</v>
+        <v>0.449036498558135</v>
       </c>
     </row>
     <row r="6">
@@ -1819,10 +1819,10 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>3.55959671080687</v>
+        <v>3.55933971292001</v>
       </c>
       <c r="D6" t="n">
-        <v>1.52196339997969</v>
+        <v>1.52193916576818</v>
       </c>
     </row>
     <row r="7">
@@ -1833,10 +1833,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="n">
-        <v>3.29235873555852</v>
+        <v>3.29299012422092</v>
       </c>
       <c r="D7" t="n">
-        <v>0.280950312695866</v>
+        <v>0.281023970144988</v>
       </c>
     </row>
     <row r="8">
@@ -1847,10 +1847,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2025859686735</v>
+        <v>3.20297728974438</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0691020427885218</v>
+        <v>0.0691138723321179</v>
       </c>
     </row>
     <row r="9">
@@ -1861,10 +1861,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>3.03305695298204</v>
+        <v>3.0335133722625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.126744121970111</v>
+        <v>0.126770841932786</v>
       </c>
     </row>
     <row r="10">
@@ -1875,10 +1875,10 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>2.94692521621535</v>
+        <v>2.94692572181785</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0839994391846857</v>
+        <v>0.084000850547</v>
       </c>
     </row>
     <row r="11">
@@ -1889,10 +1889,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>2.67860156538717</v>
+        <v>2.67894991659002</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0419688816418963</v>
+        <v>0.04197514542235</v>
       </c>
     </row>
     <row r="12">
@@ -1903,10 +1903,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>1.81461496885929</v>
+        <v>1.81456407993336</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0534914392637707</v>
+        <v>0.0534866698889865</v>
       </c>
     </row>
     <row r="13">
@@ -1917,10 +1917,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>1.40045884865932</v>
+        <v>1.40048146764749</v>
       </c>
       <c r="D13" t="n">
-        <v>0.19364127017267</v>
+        <v>0.193639893847647</v>
       </c>
     </row>
     <row r="14">
@@ -1931,10 +1931,10 @@
         <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>1.27616115610577</v>
+        <v>1.27627793711999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.356719714984737</v>
+        <v>0.356808112572214</v>
       </c>
     </row>
     <row r="15">
@@ -1945,10 +1945,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>1.25438683783237</v>
+        <v>1.25456693352899</v>
       </c>
       <c r="D15" t="n">
-        <v>0.24106015950162</v>
+        <v>0.241089866478187</v>
       </c>
     </row>
     <row r="16">
@@ -1959,10 +1959,10 @@
         <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>0.494122428436333</v>
+        <v>0.494086940416039</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0546710588271867</v>
+        <v>0.0546640015022273</v>
       </c>
     </row>
     <row r="17">
@@ -1973,10 +1973,10 @@
         <v>53</v>
       </c>
       <c r="C17" t="n">
-        <v>0.404452111589065</v>
+        <v>0.404514271002197</v>
       </c>
       <c r="D17" t="n">
-        <v>0.119356009316704</v>
+        <v>0.119374028398303</v>
       </c>
     </row>
     <row r="18">
@@ -1987,10 +1987,10 @@
         <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>0.326927283568682</v>
+        <v>0.326996599222109</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0267808047313578</v>
+        <v>0.0267843820329604</v>
       </c>
     </row>
     <row r="19">
@@ -2001,10 +2001,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>0.324127596745918</v>
+        <v>0.324087458079619</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0194578991911592</v>
+        <v>0.0194533771598683</v>
       </c>
     </row>
     <row r="20">
@@ -2015,10 +2015,10 @@
         <v>46</v>
       </c>
       <c r="C20" t="n">
-        <v>0.312515364050734</v>
+        <v>0.312523087946726</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0121710810676818</v>
+        <v>0.0121697884857879</v>
       </c>
     </row>
     <row r="21">
@@ -2029,10 +2029,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>0.311618741957831</v>
+        <v>0.311678118361911</v>
       </c>
       <c r="D21" t="n">
-        <v>0.026944690524912</v>
+        <v>0.0269425149812489</v>
       </c>
     </row>
     <row r="22">
@@ -2043,10 +2043,10 @@
         <v>11</v>
       </c>
       <c r="C22" t="n">
-        <v>0.304161632196262</v>
+        <v>0.304190892228285</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0205054566824455</v>
+        <v>0.0205040431477689</v>
       </c>
     </row>
     <row r="23">
@@ -2057,10 +2057,10 @@
         <v>18</v>
       </c>
       <c r="C23" t="n">
-        <v>0.295335450887165</v>
+        <v>0.295389801007895</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0164185430541398</v>
+        <v>0.0164209395359972</v>
       </c>
     </row>
     <row r="24">
@@ -2071,10 +2071,10 @@
         <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>0.271617161573868</v>
+        <v>0.271692713719716</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0452227912373331</v>
+        <v>0.0452396558706486</v>
       </c>
     </row>
     <row r="25">
@@ -2085,10 +2085,10 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.269796646514706</v>
+        <v>0.269707735039433</v>
       </c>
       <c r="D25" t="n">
-        <v>0.114062609061547</v>
+        <v>0.114019192404062</v>
       </c>
     </row>
     <row r="26">
@@ -2099,10 +2099,10 @@
         <v>28</v>
       </c>
       <c r="C26" t="n">
-        <v>0.260180715454235</v>
+        <v>0.260220428327975</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00968135860287472</v>
+        <v>0.00968312497329612</v>
       </c>
     </row>
     <row r="27">
@@ -2113,10 +2113,10 @@
         <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>0.244229097167627</v>
+        <v>0.244274666211047</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0566599632606738</v>
+        <v>0.0566653124413843</v>
       </c>
     </row>
     <row r="28">
@@ -2127,10 +2127,10 @@
         <v>56</v>
       </c>
       <c r="C28" t="n">
-        <v>0.233677848856114</v>
+        <v>0.233738698467344</v>
       </c>
       <c r="D28" t="n">
-        <v>0.121449640020961</v>
+        <v>0.121480725279321</v>
       </c>
     </row>
     <row r="29">
@@ -2141,10 +2141,10 @@
         <v>41</v>
       </c>
       <c r="C29" t="n">
-        <v>0.20509613095258</v>
+        <v>0.205099607290993</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0922801335946583</v>
+        <v>0.0922855481499838</v>
       </c>
     </row>
     <row r="30">
@@ -2155,10 +2155,10 @@
         <v>22</v>
       </c>
       <c r="C30" t="n">
-        <v>0.177280577180221</v>
+        <v>0.177349686375211</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0531037850044876</v>
+        <v>0.0531339957995193</v>
       </c>
     </row>
     <row r="31">
@@ -2169,10 +2169,10 @@
         <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>0.16512882342297</v>
+        <v>0.165079947125089</v>
       </c>
       <c r="D31" t="n">
-        <v>0.038389656904196</v>
+        <v>0.0383775938084506</v>
       </c>
     </row>
     <row r="32">
@@ -2183,10 +2183,10 @@
         <v>9</v>
       </c>
       <c r="C32" t="n">
-        <v>0.136011638235841</v>
+        <v>0.131794996588113</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0521300059305769</v>
+        <v>0.0661854441445949</v>
       </c>
     </row>
     <row r="33">
@@ -2197,10 +2197,10 @@
         <v>45</v>
       </c>
       <c r="C33" t="n">
-        <v>0.125367890070106</v>
+        <v>0.12542420585622</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0434058748653802</v>
+        <v>0.0434282553159728</v>
       </c>
     </row>
     <row r="34">
@@ -2211,10 +2211,10 @@
         <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>0.118243927193858</v>
+        <v>0.118278798281752</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0229964890817802</v>
+        <v>0.0230073316070332</v>
       </c>
     </row>
     <row r="35">
@@ -2225,10 +2225,10 @@
         <v>42</v>
       </c>
       <c r="C35" t="n">
-        <v>0.114824380790221</v>
+        <v>0.114820832081994</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0188727534201744</v>
+        <v>0.0188687209882469</v>
       </c>
     </row>
     <row r="36">
@@ -2239,10 +2239,10 @@
         <v>30</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0841741302901126</v>
+        <v>0.0841941838526079</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0446474285501714</v>
+        <v>0.0446584666346778</v>
       </c>
     </row>
     <row r="37">
@@ -2253,10 +2253,10 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.072734735967955</v>
+        <v>0.0727462088325313</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0112059916020685</v>
+        <v>0.0112071569070252</v>
       </c>
     </row>
     <row r="38">
@@ -2267,10 +2267,10 @@
         <v>43</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0727045168920741</v>
+        <v>0.0727340536466992</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0189350149944503</v>
+        <v>0.0189353374756009</v>
       </c>
     </row>
     <row r="39">
@@ -2281,7 +2281,7 @@
         <v>52</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0644956154866406</v>
+        <v>0.0645046244993842</v>
       </c>
       <c r="D39"/>
     </row>
@@ -2293,7 +2293,7 @@
         <v>23</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0432567644968339</v>
+        <v>0.0432617797324005</v>
       </c>
       <c r="D40"/>
     </row>
@@ -2305,10 +2305,10 @@
         <v>60</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0429239861368291</v>
+        <v>0.0429195928342779</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00886888518612882</v>
+        <v>0.00886564634343576</v>
       </c>
     </row>
     <row r="42">
@@ -2319,10 +2319,10 @@
         <v>62</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0419484996263832</v>
+        <v>0.0419490196625307</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0084232475509638</v>
+        <v>0.00842450834252437</v>
       </c>
     </row>
     <row r="43">
@@ -2333,10 +2333,10 @@
         <v>31</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0397237122959858</v>
+        <v>0.0397120971304546</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00947299326764446</v>
+        <v>0.00946994220344433</v>
       </c>
     </row>
     <row r="44">
@@ -2347,10 +2347,10 @@
         <v>36</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0388027675322517</v>
+        <v>0.0388100350061249</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00602111743888595</v>
+        <v>0.00603708597332847</v>
       </c>
     </row>
     <row r="45">
@@ -2361,10 +2361,10 @@
         <v>26</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0354344461474857</v>
+        <v>0.035442680191661</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00279457201696507</v>
+        <v>0.00279386431538608</v>
       </c>
     </row>
     <row r="46">
@@ -2375,7 +2375,7 @@
         <v>59</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0346546465796339</v>
+        <v>0.0346662216542633</v>
       </c>
       <c r="D46"/>
     </row>
@@ -2387,7 +2387,7 @@
         <v>55</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0236047835160865</v>
+        <v>0.0236057392249564</v>
       </c>
       <c r="D47"/>
     </row>
@@ -2399,10 +2399,10 @@
         <v>67</v>
       </c>
       <c r="C48" t="n">
-        <v>0.022240134272346</v>
+        <v>0.0222469367845104</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0117897263172993</v>
+        <v>0.0117923596586746</v>
       </c>
     </row>
     <row r="49">
@@ -2413,10 +2413,10 @@
         <v>39</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0177592349597235</v>
+        <v>0.0177613048734907</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00665330089369151</v>
+        <v>0.00665097836036566</v>
       </c>
     </row>
     <row r="50">
@@ -2427,10 +2427,10 @@
         <v>63</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0168685092718702</v>
+        <v>0.0168710295960285</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0018493841627185</v>
+        <v>0.00185626263997204</v>
       </c>
     </row>
     <row r="51">
@@ -2441,10 +2441,10 @@
         <v>66</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0110229607155072</v>
+        <v>0.0110269635835274</v>
       </c>
       <c r="D51" t="n">
-        <v>0.000905538955255288</v>
+        <v>0.000904039234368312</v>
       </c>
     </row>
     <row r="52">
@@ -2455,10 +2455,10 @@
         <v>64</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00626271921364477</v>
+        <v>0.00626691914387329</v>
       </c>
       <c r="D52" t="n">
-        <v>0.00246046009079724</v>
+        <v>0.00246182046766041</v>
       </c>
     </row>
     <row r="53">
@@ -2469,7 +2469,7 @@
         <v>50</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00456492308458384</v>
+        <v>0.00456556146634004</v>
       </c>
       <c r="D53"/>
     </row>
@@ -2481,7 +2481,7 @@
         <v>69</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00445399696458224</v>
+        <v>0.00445174472627557</v>
       </c>
       <c r="D54"/>
     </row>
@@ -2493,7 +2493,7 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00417539182597359</v>
+        <v>0.00417770053660579</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -3241,10 +3241,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>27.30072698065</v>
+        <v>27.3021584592945</v>
       </c>
       <c r="D2" t="n">
-        <v>0.293765573683471</v>
+        <v>0.293783568780292</v>
       </c>
     </row>
     <row r="3">
@@ -3255,10 +3255,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>14.3092141034448</v>
+        <v>14.3095521024706</v>
       </c>
       <c r="D3" t="n">
-        <v>0.213874944849593</v>
+        <v>0.213880919026889</v>
       </c>
     </row>
     <row r="4">
@@ -3269,10 +3269,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>11.7116743025949</v>
+        <v>11.7128284465102</v>
       </c>
       <c r="D4" t="n">
-        <v>0.352416595006116</v>
+        <v>0.35245303862179</v>
       </c>
     </row>
     <row r="5">
@@ -3283,10 +3283,10 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>9.10757150887906</v>
+        <v>9.10818368095627</v>
       </c>
       <c r="D5" t="n">
-        <v>1.42647763426101</v>
+        <v>1.42655083749577</v>
       </c>
     </row>
     <row r="6">
@@ -3297,10 +3297,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>7.72448020448984</v>
+        <v>7.72488329752463</v>
       </c>
       <c r="D6" t="n">
-        <v>0.200824954047094</v>
+        <v>0.200833280369296</v>
       </c>
     </row>
     <row r="7">
@@ -3311,10 +3311,10 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>6.05207338627771</v>
+        <v>6.05232779459891</v>
       </c>
       <c r="D7" t="n">
-        <v>0.148814703016456</v>
+        <v>0.148822561759526</v>
       </c>
     </row>
     <row r="8">
@@ -3325,10 +3325,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>4.93576622200503</v>
+        <v>4.93592282166846</v>
       </c>
       <c r="D8" t="n">
-        <v>0.248538990846405</v>
+        <v>0.248549954187797</v>
       </c>
     </row>
     <row r="9">
@@ -3339,10 +3339,10 @@
         <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>1.94089697836368</v>
+        <v>1.94103180627408</v>
       </c>
       <c r="D9" t="n">
-        <v>0.284651872296322</v>
+        <v>0.284665040070486</v>
       </c>
     </row>
     <row r="10">
@@ -3353,10 +3353,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>1.87225351126259</v>
+        <v>1.87255155631141</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0375882363455062</v>
+        <v>0.0375949430856047</v>
       </c>
     </row>
     <row r="11">
@@ -3367,10 +3367,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>1.67001414281031</v>
+        <v>1.67015524234597</v>
       </c>
       <c r="D11" t="n">
-        <v>0.198853841499702</v>
+        <v>0.198881530966516</v>
       </c>
     </row>
     <row r="12">
@@ -3381,10 +3381,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.64698391335536</v>
+        <v>1.64714137079565</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0407056647087472</v>
+        <v>0.0407097333684327</v>
       </c>
     </row>
     <row r="13">
@@ -3395,10 +3395,10 @@
         <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>1.60019016147947</v>
+        <v>1.60042867122582</v>
       </c>
       <c r="D13" t="n">
-        <v>0.906062920637164</v>
+        <v>0.906197886870619</v>
       </c>
     </row>
     <row r="14">
@@ -3409,10 +3409,10 @@
         <v>45</v>
       </c>
       <c r="C14" t="n">
-        <v>1.50301322821784</v>
+        <v>1.50307371926811</v>
       </c>
       <c r="D14" t="n">
-        <v>0.855411052568974</v>
+        <v>0.855436440752977</v>
       </c>
     </row>
     <row r="15">
@@ -3423,10 +3423,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>1.47291073996992</v>
+        <v>1.47309043645052</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0349346089423087</v>
+        <v>0.0349375182274038</v>
       </c>
     </row>
     <row r="16">
@@ -3437,10 +3437,10 @@
         <v>44</v>
       </c>
       <c r="C16" t="n">
-        <v>0.922565416238923</v>
+        <v>0.922486555773467</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0491641010685336</v>
+        <v>0.0491541307679486</v>
       </c>
     </row>
     <row r="17">
@@ -3451,10 +3451,10 @@
         <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>0.837781175743282</v>
+        <v>0.837883196212626</v>
       </c>
       <c r="D17" t="n">
-        <v>0.108916151041769</v>
+        <v>0.108929752240514</v>
       </c>
     </row>
     <row r="18">
@@ -3465,10 +3465,10 @@
         <v>66</v>
       </c>
       <c r="C18" t="n">
-        <v>0.825813218255719</v>
+        <v>0.82591185495775</v>
       </c>
       <c r="D18" t="n">
-        <v>0.351181612112213</v>
+        <v>0.35122184520013</v>
       </c>
     </row>
     <row r="19">
@@ -3479,10 +3479,10 @@
         <v>46</v>
       </c>
       <c r="C19" t="n">
-        <v>0.37610308904846</v>
+        <v>0.376096031263179</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0103826239151434</v>
+        <v>0.0103818561777095</v>
       </c>
     </row>
     <row r="20">
@@ -3493,10 +3493,10 @@
         <v>28</v>
       </c>
       <c r="C20" t="n">
-        <v>0.337290612742807</v>
+        <v>0.337357290297562</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0101778734838618</v>
+        <v>0.0101795486820938</v>
       </c>
     </row>
     <row r="21">
@@ -3507,10 +3507,10 @@
         <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>0.320268305441944</v>
+        <v>0.320354889679107</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0298883686993958</v>
+        <v>0.0299025682995732</v>
       </c>
     </row>
     <row r="22">
@@ -3521,10 +3521,10 @@
         <v>53</v>
       </c>
       <c r="C22" t="n">
-        <v>0.287933458539462</v>
+        <v>0.287933061959075</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0528307738210819</v>
+        <v>0.0528326269994577</v>
       </c>
     </row>
     <row r="23">
@@ -3535,10 +3535,10 @@
         <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>0.269857641185242</v>
+        <v>0.269881171537894</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0257237604284908</v>
+        <v>0.0257283054067146</v>
       </c>
     </row>
     <row r="24">
@@ -3549,10 +3549,10 @@
         <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>0.269189307732421</v>
+        <v>0.263324565141488</v>
       </c>
       <c r="D24" t="n">
-        <v>0.062650809176541</v>
+        <v>0.0690289434094733</v>
       </c>
     </row>
     <row r="25">
@@ -3563,10 +3563,10 @@
         <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>0.262869913040822</v>
+        <v>0.262847259509559</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0463824129946913</v>
+        <v>0.0463815934658905</v>
       </c>
     </row>
     <row r="26">
@@ -3577,10 +3577,10 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.256010021887065</v>
+        <v>0.256010594969919</v>
       </c>
       <c r="D26" t="n">
-        <v>0.142569995913742</v>
+        <v>0.142570873400529</v>
       </c>
     </row>
     <row r="27">
@@ -3591,10 +3591,10 @@
         <v>67</v>
       </c>
       <c r="C27" t="n">
-        <v>0.23921632210371</v>
+        <v>0.239204193438333</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0417621481813443</v>
+        <v>0.0417595766071978</v>
       </c>
     </row>
     <row r="28">
@@ -3605,10 +3605,10 @@
         <v>56</v>
       </c>
       <c r="C28" t="n">
-        <v>0.237137617682225</v>
+        <v>0.237160143513279</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0956764266202067</v>
+        <v>0.095693633147602</v>
       </c>
     </row>
     <row r="29">
@@ -3619,10 +3619,10 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>0.197913731126486</v>
+        <v>0.197923706352554</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0120282215012531</v>
+        <v>0.012025586589176</v>
       </c>
     </row>
     <row r="30">
@@ -3633,10 +3633,10 @@
         <v>62</v>
       </c>
       <c r="C30" t="n">
-        <v>0.147332339944141</v>
+        <v>0.1473592710119</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0411378134408208</v>
+        <v>0.0411447289052997</v>
       </c>
     </row>
     <row r="31">
@@ -3647,10 +3647,10 @@
         <v>22</v>
       </c>
       <c r="C31" t="n">
-        <v>0.145481826633027</v>
+        <v>0.145512884709484</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0376126041665956</v>
+        <v>0.0376233712356787</v>
       </c>
     </row>
     <row r="32">
@@ -3661,10 +3661,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.139505551421257</v>
+        <v>0.139484768419922</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0399304061372491</v>
+        <v>0.0399268761481637</v>
       </c>
     </row>
     <row r="33">
@@ -3675,10 +3675,10 @@
         <v>21</v>
       </c>
       <c r="C33" t="n">
-        <v>0.115253167022988</v>
+        <v>0.115259530963283</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0128640684497051</v>
+        <v>0.0128622807945025</v>
       </c>
     </row>
     <row r="34">
@@ -3689,10 +3689,10 @@
         <v>41</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0963099736050754</v>
+        <v>0.0963166977714309</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0240246765362426</v>
+        <v>0.0240223859892184</v>
       </c>
     </row>
     <row r="35">
@@ -3703,10 +3703,10 @@
         <v>42</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0956412237451183</v>
+        <v>0.0956425607847479</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0218168532658387</v>
+        <v>0.0218209379727358</v>
       </c>
     </row>
     <row r="36">
@@ -3717,10 +3717,10 @@
         <v>60</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0922541681032187</v>
+        <v>0.092229430189208</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0213534318423919</v>
+        <v>0.0213467128775279</v>
       </c>
     </row>
     <row r="37">
@@ -3731,10 +3731,10 @@
         <v>59</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0772385267893631</v>
+        <v>0.077248192128975</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0267596877267097</v>
+        <v>0.0267612577520961</v>
       </c>
     </row>
     <row r="38">
@@ -3745,10 +3745,10 @@
         <v>33</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0722433067893351</v>
+        <v>0.0722479266771331</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0137011317897582</v>
+        <v>0.0136998026258666</v>
       </c>
     </row>
     <row r="39">
@@ -3759,10 +3759,10 @@
         <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0603590471360507</v>
+        <v>0.0603581476749671</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00785656459814112</v>
+        <v>0.00785715219699309</v>
       </c>
     </row>
     <row r="40">
@@ -3773,7 +3773,7 @@
         <v>23</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0593205277395794</v>
+        <v>0.0593003351933941</v>
       </c>
       <c r="D40"/>
     </row>
@@ -3785,7 +3785,7 @@
         <v>52</v>
       </c>
       <c r="C41" t="n">
-        <v>0.056160413986644</v>
+        <v>0.0561568593925275</v>
       </c>
       <c r="D41"/>
     </row>
@@ -3797,10 +3797,10 @@
         <v>26</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0520046707722159</v>
+        <v>0.051996768370385</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00243539410505951</v>
+        <v>0.0024350882234929</v>
       </c>
     </row>
     <row r="43">
@@ -3811,7 +3811,7 @@
         <v>80</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0490590066941733</v>
+        <v>0.0490609434067745</v>
       </c>
       <c r="D43"/>
     </row>
@@ -3823,10 +3823,10 @@
         <v>12</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0472509669109021</v>
+        <v>0.0472553382307141</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00574510365646315</v>
+        <v>0.00574223356787872</v>
       </c>
     </row>
     <row r="45">
@@ -3837,10 +3837,10 @@
         <v>30</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0407466874510456</v>
+        <v>0.0407403452285472</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00453607352798934</v>
+        <v>0.00453519198596773</v>
       </c>
     </row>
     <row r="46">
@@ -3851,10 +3851,10 @@
         <v>43</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0384268832979816</v>
+        <v>0.0384374599913225</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00845349612281678</v>
+        <v>0.00847325561293235</v>
       </c>
     </row>
     <row r="47">
@@ -3865,10 +3865,10 @@
         <v>31</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0294899533512826</v>
+        <v>0.0294847543545942</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00213860899230777</v>
+        <v>0.00213711749843435</v>
       </c>
     </row>
     <row r="48">
@@ -3879,7 +3879,7 @@
         <v>58</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0269702737730757</v>
+        <v>0.0269629826636687</v>
       </c>
       <c r="D48"/>
     </row>
@@ -3891,7 +3891,7 @@
         <v>61</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0141182839363913</v>
+        <v>0.014109021316969</v>
       </c>
       <c r="D49"/>
     </row>
@@ -3903,7 +3903,7 @@
         <v>39</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0134349598266843</v>
+        <v>0.0134452876788458</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
         <v>36</v>
       </c>
       <c r="C51" t="n">
-        <v>0.00970645033349896</v>
+        <v>0.00970008219727315</v>
       </c>
       <c r="D51"/>
     </row>
@@ -3929,7 +3929,7 @@
         <v>72</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0092367430844133</v>
+        <v>0.00924358326246369</v>
       </c>
       <c r="D52"/>
     </row>
@@ -3941,10 +3941,10 @@
         <v>63</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00861046675229908</v>
+        <v>0.00861064353607791</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00015075548641178</v>
+        <v>0.000146537064010291</v>
       </c>
     </row>
     <row r="54">
@@ -3955,7 +3955,7 @@
         <v>50</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0077281000317206</v>
+        <v>0.00772885571213875</v>
       </c>
       <c r="D54"/>
     </row>
@@ -3967,7 +3967,7 @@
         <v>20</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00335873995667107</v>
+        <v>0.00336152998668265</v>
       </c>
       <c r="D55"/>
     </row>
@@ -3979,7 +3979,7 @@
         <v>34</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00251926317107116</v>
+        <v>0.00252093942304079</v>
       </c>
       <c r="D56"/>
     </row>
@@ -3991,7 +3991,7 @@
         <v>64</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00251926317107116</v>
+        <v>0.00252093942304079</v>
       </c>
       <c r="D57"/>
     </row>
@@ -4028,10 +4028,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>22.8613351869435</v>
+        <v>22.8598954626742</v>
       </c>
       <c r="D2" t="n">
-        <v>0.480337532839626</v>
+        <v>0.481636103431631</v>
       </c>
     </row>
     <row r="3">
@@ -4042,10 +4042,10 @@
         <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>10.8172862772102</v>
+        <v>10.8202104841912</v>
       </c>
       <c r="D3" t="n">
-        <v>2.45815385280945</v>
+        <v>2.45908224707151</v>
       </c>
     </row>
     <row r="4">
@@ -4056,10 +4056,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>8.13866992397505</v>
+        <v>8.13792105432136</v>
       </c>
       <c r="D4" t="n">
-        <v>0.367292521595162</v>
+        <v>0.367249869019118</v>
       </c>
     </row>
     <row r="5">
@@ -4070,10 +4070,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>7.51924147469028</v>
+        <v>7.51902779710455</v>
       </c>
       <c r="D5" t="n">
-        <v>0.537059410224198</v>
+        <v>0.53703158755585</v>
       </c>
     </row>
     <row r="6">
@@ -4084,10 +4084,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>7.03162985000902</v>
+        <v>7.03188939142277</v>
       </c>
       <c r="D6" t="n">
-        <v>0.114487677542065</v>
+        <v>0.114498042682043</v>
       </c>
     </row>
     <row r="7">
@@ -4098,10 +4098,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>6.49359277867455</v>
+        <v>6.49367459782191</v>
       </c>
       <c r="D7" t="n">
-        <v>0.194390308782477</v>
+        <v>0.194390163645976</v>
       </c>
     </row>
     <row r="8">
@@ -4112,10 +4112,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>5.25248131316863</v>
+        <v>5.25404288182796</v>
       </c>
       <c r="D8" t="n">
-        <v>2.61034097186155</v>
+        <v>2.61111821224153</v>
       </c>
     </row>
     <row r="9">
@@ -4126,10 +4126,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>4.31668086481731</v>
+        <v>4.31637807066618</v>
       </c>
       <c r="D9" t="n">
-        <v>0.339336336595216</v>
+        <v>0.339302077092949</v>
       </c>
     </row>
     <row r="10">
@@ -4140,10 +4140,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>4.06673828943547</v>
+        <v>4.06641464005393</v>
       </c>
       <c r="D10" t="n">
-        <v>0.502934125220771</v>
+        <v>0.502880044043259</v>
       </c>
     </row>
     <row r="11">
@@ -4154,10 +4154,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>3.73737619650052</v>
+        <v>3.73660823307264</v>
       </c>
       <c r="D11" t="n">
-        <v>1.14298852723429</v>
+        <v>1.14275293472737</v>
       </c>
     </row>
     <row r="12">
@@ -4168,10 +4168,10 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>3.51945173088862</v>
+        <v>3.51911241763259</v>
       </c>
       <c r="D12" t="n">
-        <v>0.337852602807758</v>
+        <v>0.337806653408618</v>
       </c>
     </row>
     <row r="13">
@@ -4182,10 +4182,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>2.20614405342171</v>
+        <v>2.20607468352745</v>
       </c>
       <c r="D13" t="n">
-        <v>0.194223998054566</v>
+        <v>0.194223892782296</v>
       </c>
     </row>
     <row r="14">
@@ -4196,10 +4196,10 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0635971340085</v>
+        <v>2.06376020806829</v>
       </c>
       <c r="D14" t="n">
-        <v>0.296137059461325</v>
+        <v>0.296177621823349</v>
       </c>
     </row>
     <row r="15">
@@ -4210,10 +4210,10 @@
         <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0221044582193</v>
+        <v>2.02235696353868</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0715557406952814</v>
+        <v>0.071571063185759</v>
       </c>
     </row>
     <row r="16">
@@ -4224,10 +4224,10 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>1.29271025057729</v>
+        <v>1.29250797810644</v>
       </c>
       <c r="D16" t="n">
-        <v>0.527349259694941</v>
+        <v>0.527251453330294</v>
       </c>
     </row>
     <row r="17">
@@ -4238,10 +4238,10 @@
         <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>1.22104922075308</v>
+        <v>1.22074625744503</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0969448052490019</v>
+        <v>0.0969124714216725</v>
       </c>
     </row>
     <row r="18">
@@ -4252,10 +4252,10 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>1.17130231702973</v>
+        <v>1.17126624272846</v>
       </c>
       <c r="D18" t="n">
-        <v>0.112478569011275</v>
+        <v>0.112466191172787</v>
       </c>
     </row>
     <row r="19">
@@ -4266,10 +4266,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>1.11397760268898</v>
+        <v>1.11370615270444</v>
       </c>
       <c r="D19" t="n">
-        <v>0.190043655700727</v>
+        <v>0.189987511302288</v>
       </c>
     </row>
     <row r="20">
@@ -4280,10 +4280,10 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9351382017884</v>
+        <v>0.93506297308654</v>
       </c>
       <c r="D20" t="n">
-        <v>0.402167127338207</v>
+        <v>0.402110589883817</v>
       </c>
     </row>
     <row r="21">
@@ -4294,10 +4294,10 @@
         <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>0.703742781394376</v>
+        <v>0.703616952247296</v>
       </c>
       <c r="D21" t="n">
-        <v>0.124972059118779</v>
+        <v>0.124934565143439</v>
       </c>
     </row>
     <row r="22">
@@ -4308,10 +4308,10 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.660316270064112</v>
+        <v>0.66027619886335</v>
       </c>
       <c r="D22" t="n">
-        <v>0.464677595584426</v>
+        <v>0.464650200299601</v>
       </c>
     </row>
     <row r="23">
@@ -4322,10 +4322,10 @@
         <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>0.646192043529836</v>
+        <v>0.646208425606298</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0493176730090856</v>
+        <v>0.0493180758996454</v>
       </c>
     </row>
     <row r="24">
@@ -4336,7 +4336,7 @@
         <v>29</v>
       </c>
       <c r="C24" t="n">
-        <v>0.536983711965485</v>
+        <v>0.537012201898169</v>
       </c>
       <c r="D24"/>
     </row>
@@ -4348,10 +4348,10 @@
         <v>26</v>
       </c>
       <c r="C25" t="n">
-        <v>0.489098136759377</v>
+        <v>0.48904168293091</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0318588748514684</v>
+        <v>0.0318549827304498</v>
       </c>
     </row>
     <row r="26">
@@ -4362,10 +4362,10 @@
         <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>0.234581950574792</v>
+        <v>0.234622241641747</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0117104269527998</v>
+        <v>0.0117115568617313</v>
       </c>
     </row>
     <row r="27">
@@ -4376,10 +4376,10 @@
         <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>0.195495468788093</v>
+        <v>0.195453966811647</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0513841841070872</v>
+        <v>0.0513702577869165</v>
       </c>
     </row>
     <row r="28">
@@ -4390,10 +4390,10 @@
         <v>36</v>
       </c>
       <c r="C28" t="n">
-        <v>0.182014830657508</v>
+        <v>0.181970727723392</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0349022452918419</v>
+        <v>0.034894042293741</v>
       </c>
     </row>
     <row r="29">
@@ -4404,10 +4404,10 @@
         <v>31</v>
       </c>
       <c r="C29" t="n">
-        <v>0.152038017978606</v>
+        <v>0.152048527497874</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0158166230194658</v>
+        <v>0.0158197375722674</v>
       </c>
     </row>
     <row r="30">
@@ -4418,10 +4418,10 @@
         <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>0.058479158420469</v>
+        <v>0.0584890649651441</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0241762986525958</v>
+        <v>0.0241860445783233</v>
       </c>
     </row>
     <row r="31">
@@ -4432,10 +4432,10 @@
         <v>39</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0559662114056922</v>
+        <v>0.0559618281812285</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0122649839704664</v>
+        <v>0.0122628547439925</v>
       </c>
     </row>
     <row r="32">
@@ -4446,7 +4446,7 @@
         <v>40</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0364025410088863</v>
+        <v>0.0364207753727237</v>
       </c>
       <c r="D32"/>
     </row>
@@ -4458,10 +4458,10 @@
         <v>41</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0305625371710683</v>
+        <v>0.0305612688825991</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0174926602317377</v>
+        <v>0.0174894866909971</v>
       </c>
     </row>
     <row r="34">
@@ -4472,10 +4472,10 @@
         <v>30</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0289576992983796</v>
+        <v>0.0289658400002355</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0122399849569952</v>
+        <v>0.0122438113694564</v>
       </c>
     </row>
     <row r="35">
@@ -4486,10 +4486,10 @@
         <v>42</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0269381306965604</v>
+        <v>0.0269516051342507</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00210168804925245</v>
+        <v>0.00210284985716427</v>
       </c>
     </row>
     <row r="36">
@@ -4500,7 +4500,7 @@
         <v>43</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0254816133807589</v>
+        <v>0.025494519152903</v>
       </c>
       <c r="D36"/>
     </row>
@@ -4512,10 +4512,10 @@
         <v>44</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0244015657587125</v>
+        <v>0.0244092592280399</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0022490266463593</v>
+        <v>0.00225101742254739</v>
       </c>
     </row>
     <row r="38">
@@ -4526,7 +4526,7 @@
         <v>45</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0232820762051372</v>
+        <v>0.02327701937604</v>
       </c>
       <c r="D38"/>
     </row>
@@ -4538,10 +4538,10 @@
         <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0205733366081001</v>
+        <v>0.0205814575265539</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00381634393833494</v>
+        <v>0.003818566330653</v>
       </c>
     </row>
     <row r="40">
@@ -4552,10 +4552,10 @@
         <v>32</v>
       </c>
       <c r="C40" t="n">
-        <v>0.020056576451302</v>
+        <v>0.0200538186463997</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0026355359957798</v>
+        <v>0.00263383868281985</v>
       </c>
     </row>
     <row r="41">
@@ -4566,10 +4566,10 @@
         <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0193286720622474</v>
+        <v>0.0193252756557258</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0026368186423035</v>
+        <v>0.00263637382526216</v>
       </c>
     </row>
     <row r="42">
@@ -4580,10 +4580,10 @@
         <v>47</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0176222771203525</v>
+        <v>0.0176207777967935</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0102243149460346</v>
+        <v>0.0102241940971423</v>
       </c>
     </row>
     <row r="43">
@@ -4594,7 +4594,7 @@
         <v>48</v>
       </c>
       <c r="C43" t="n">
-        <v>0.00844695018641817</v>
+        <v>0.00844623544307777</v>
       </c>
       <c r="D43"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>49</v>
       </c>
       <c r="C44" t="n">
-        <v>0.00528427410795247</v>
+        <v>0.00528488768283364</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00038177099680891</v>
+        <v>0.000383613859213234</v>
       </c>
     </row>
     <row r="45">
@@ -4620,7 +4620,7 @@
         <v>50</v>
       </c>
       <c r="C45" t="n">
-        <v>0.00436837105125096</v>
+        <v>0.00437054970393546</v>
       </c>
       <c r="D45"/>
     </row>
@@ -4632,7 +4632,7 @@
         <v>51</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00364023048296556</v>
+        <v>0.00364200671326161</v>
       </c>
       <c r="D46"/>
     </row>
@@ -4644,7 +4644,7 @@
         <v>34</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0031626760784657</v>
+        <v>0.00316134776024414</v>
       </c>
       <c r="D47"/>
     </row>
@@ -4656,7 +4656,7 @@
         <v>52</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0031626760784657</v>
+        <v>0.00316134776024414</v>
       </c>
       <c r="D48"/>
     </row>
@@ -4668,7 +4668,7 @@
         <v>53</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00291208991468017</v>
+        <v>0.00291369980262364</v>
       </c>
       <c r="D49"/>
     </row>
@@ -4705,10 +4705,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>35.3042071065908</v>
+        <v>35.2833955838753</v>
       </c>
       <c r="D2" t="n">
-        <v>0.835103038611713</v>
+        <v>0.834439311562662</v>
       </c>
     </row>
     <row r="3">
@@ -4719,10 +4719,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>20.3638802869431</v>
+        <v>20.3726252576049</v>
       </c>
       <c r="D3" t="n">
-        <v>0.401482699031722</v>
+        <v>0.402864313882846</v>
       </c>
     </row>
     <row r="4">
@@ -4733,10 +4733,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>8.26327382827462</v>
+        <v>8.27579797420807</v>
       </c>
       <c r="D4" t="n">
-        <v>1.83069181913315</v>
+        <v>1.83352029366796</v>
       </c>
     </row>
     <row r="5">
@@ -4747,10 +4747,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>5.96858796391916</v>
+        <v>5.97114773286654</v>
       </c>
       <c r="D5" t="n">
-        <v>0.166071329229273</v>
+        <v>0.166150040239882</v>
       </c>
     </row>
     <row r="6">
@@ -4761,10 +4761,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>4.56674681022025</v>
+        <v>4.56837463672266</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1719739669076</v>
+        <v>0.172006319902881</v>
       </c>
     </row>
     <row r="7">
@@ -4775,10 +4775,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5259305656663</v>
+        <v>4.52785103200182</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0902610659435204</v>
+        <v>0.0902945887816594</v>
       </c>
     </row>
     <row r="8">
@@ -4789,10 +4789,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>4.14160224736797</v>
+        <v>4.1422831318881</v>
       </c>
       <c r="D8" t="n">
-        <v>0.181749004281561</v>
+        <v>0.181760759661738</v>
       </c>
     </row>
     <row r="9">
@@ -4803,10 +4803,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>2.00207706773129</v>
+        <v>2.00270865730439</v>
       </c>
       <c r="D9" t="n">
-        <v>0.20502442970376</v>
+        <v>0.204976409443648</v>
       </c>
     </row>
     <row r="10">
@@ -4817,10 +4817,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>1.89449433606883</v>
+        <v>1.8945396722394</v>
       </c>
       <c r="D10" t="n">
-        <v>0.814750001263307</v>
+        <v>0.814784764140172</v>
       </c>
     </row>
     <row r="11">
@@ -4831,10 +4831,10 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>1.21352271950406</v>
+        <v>1.21414758021416</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0584750345677766</v>
+        <v>0.0585218941009866</v>
       </c>
     </row>
     <row r="12">
@@ -4845,10 +4845,10 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>1.17865054036816</v>
+        <v>1.17937209081257</v>
       </c>
       <c r="D12" t="n">
-        <v>0.152413586829637</v>
+        <v>0.152485274640383</v>
       </c>
     </row>
     <row r="13">
@@ -4859,10 +4859,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>1.17319093691089</v>
+        <v>1.17333691916472</v>
       </c>
       <c r="D13" t="n">
-        <v>0.078664682449261</v>
+        <v>0.078654647683715</v>
       </c>
     </row>
     <row r="14">
@@ -4873,10 +4873,10 @@
         <v>48</v>
       </c>
       <c r="C14" t="n">
-        <v>0.911457702861373</v>
+        <v>0.910770455691572</v>
       </c>
       <c r="D14" t="n">
-        <v>0.132453907491433</v>
+        <v>0.132662553886966</v>
       </c>
     </row>
     <row r="15">
@@ -4887,10 +4887,10 @@
         <v>55</v>
       </c>
       <c r="C15" t="n">
-        <v>0.902268494818009</v>
+        <v>0.901958939426524</v>
       </c>
       <c r="D15" t="n">
-        <v>0.619793329917475</v>
+        <v>0.619599519354905</v>
       </c>
     </row>
     <row r="16">
@@ -4901,10 +4901,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>0.789236539172532</v>
+        <v>0.789800414963352</v>
       </c>
       <c r="D16" t="n">
-        <v>0.188286693164716</v>
+        <v>0.188448622309343</v>
       </c>
     </row>
     <row r="17">
@@ -4915,10 +4915,10 @@
         <v>56</v>
       </c>
       <c r="C17" t="n">
-        <v>0.757690462561123</v>
+        <v>0.757375474272256</v>
       </c>
       <c r="D17" t="n">
-        <v>0.232820381922534</v>
+        <v>0.232616537343211</v>
       </c>
     </row>
     <row r="18">
@@ -4929,10 +4929,10 @@
         <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.637198519282894</v>
+        <v>0.638069273111386</v>
       </c>
       <c r="D18" t="n">
-        <v>0.253002161971351</v>
+        <v>0.253366646523741</v>
       </c>
     </row>
     <row r="19">
@@ -4943,10 +4943,10 @@
         <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>0.57501431057039</v>
+        <v>0.575175464475067</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0474068984273131</v>
+        <v>0.0474216348281234</v>
       </c>
     </row>
     <row r="20">
@@ -4957,7 +4957,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.538804736176943</v>
+        <v>0.538711286626458</v>
       </c>
       <c r="D20"/>
     </row>
@@ -4969,10 +4969,10 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>0.388431324470689</v>
+        <v>0.388895838090914</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0573692570991049</v>
+        <v>0.057445907169787</v>
       </c>
     </row>
     <row r="22">
@@ -4983,10 +4983,10 @@
         <v>53</v>
       </c>
       <c r="C22" t="n">
-        <v>0.387830093424562</v>
+        <v>0.387742435926616</v>
       </c>
       <c r="D22" t="n">
-        <v>0.162790426953632</v>
+        <v>0.162759820132935</v>
       </c>
     </row>
     <row r="23">
@@ -4997,10 +4997,10 @@
         <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>0.353995602227142</v>
+        <v>0.354421123670223</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0460650820835099</v>
+        <v>0.046139952032642</v>
       </c>
     </row>
     <row r="24">
@@ -5011,10 +5011,10 @@
         <v>21</v>
       </c>
       <c r="C24" t="n">
-        <v>0.323777838833309</v>
+        <v>0.323916794302982</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0224449371466319</v>
+        <v>0.0224610762133281</v>
       </c>
     </row>
     <row r="25">
@@ -5025,10 +5025,10 @@
         <v>44</v>
       </c>
       <c r="C25" t="n">
-        <v>0.306349923101333</v>
+        <v>0.306298162095326</v>
       </c>
       <c r="D25" t="n">
-        <v>0.039506758019685</v>
+        <v>0.0394995014382875</v>
       </c>
     </row>
     <row r="26">
@@ -5039,10 +5039,10 @@
         <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>0.29468313455369</v>
+        <v>0.294836098666361</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0405332162348049</v>
+        <v>0.0405496999700145</v>
       </c>
     </row>
     <row r="27">
@@ -5053,10 +5053,10 @@
         <v>28</v>
       </c>
       <c r="C27" t="n">
-        <v>0.287640661272779</v>
+        <v>0.287768404300074</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0259380190164108</v>
+        <v>0.0259426648276639</v>
       </c>
     </row>
     <row r="28">
@@ -5067,10 +5067,10 @@
         <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>0.271338918497294</v>
+        <v>0.271458479754603</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0248233274360269</v>
+        <v>0.0248368148633594</v>
       </c>
     </row>
     <row r="29">
@@ -5081,10 +5081,10 @@
         <v>20</v>
       </c>
       <c r="C29" t="n">
-        <v>0.212536861470251</v>
+        <v>0.212489241049858</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0277448059789946</v>
+        <v>0.0277291126964983</v>
       </c>
     </row>
     <row r="30">
@@ -5095,7 +5095,7 @@
         <v>40</v>
       </c>
       <c r="C30" t="n">
-        <v>0.195109464711988</v>
+        <v>0.194871385369692</v>
       </c>
       <c r="D30"/>
     </row>
@@ -5107,10 +5107,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>0.169785104454905</v>
+        <v>0.169805078010923</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0560362338182595</v>
+        <v>0.0560356771405669</v>
       </c>
     </row>
     <row r="32">
@@ -5121,10 +5121,10 @@
         <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>0.126737791910195</v>
+        <v>0.126769924546766</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0789306236296212</v>
+        <v>0.0789363207389311</v>
       </c>
     </row>
     <row r="33">
@@ -5135,10 +5135,10 @@
         <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>0.119665996614518</v>
+        <v>0.119712325037842</v>
       </c>
       <c r="D33" t="n">
-        <v>0.021600350577494</v>
+        <v>0.0216224529967841</v>
       </c>
     </row>
     <row r="34">
@@ -5149,10 +5149,10 @@
         <v>39</v>
       </c>
       <c r="C34" t="n">
-        <v>0.119290259646546</v>
+        <v>0.119276693116272</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0223677914749913</v>
+        <v>0.0223592105658954</v>
       </c>
     </row>
     <row r="35">
@@ -5163,10 +5163,10 @@
         <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>0.102528965648493</v>
+        <v>0.091378390003555</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0183158163231817</v>
+        <v>0.0202266071602769</v>
       </c>
     </row>
     <row r="36">
@@ -5177,10 +5177,10 @@
         <v>22</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0714626802344464</v>
+        <v>0.0715598554183471</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00653259779790635</v>
+        <v>0.00654621341616197</v>
       </c>
     </row>
     <row r="37">
@@ -5191,7 +5191,7 @@
         <v>29</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0619908910045344</v>
+        <v>0.062051535152785</v>
       </c>
       <c r="D37"/>
     </row>
@@ -5203,10 +5203,10 @@
         <v>42</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0618292306930382</v>
+        <v>0.0618814756326</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00825564344280097</v>
+        <v>0.00825995041681047</v>
       </c>
     </row>
     <row r="39">
@@ -5217,7 +5217,7 @@
         <v>50</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0580508425779555</v>
+        <v>0.0580969394916194</v>
       </c>
       <c r="D39"/>
     </row>
@@ -5229,7 +5229,7 @@
         <v>57</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0561355700913525</v>
+        <v>0.0561571738230256</v>
       </c>
       <c r="D40"/>
     </row>
@@ -5241,10 +5241,10 @@
         <v>41</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0484986124225799</v>
+        <v>0.048503718887213</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00916381292962546</v>
+        <v>0.00917211959844195</v>
       </c>
     </row>
     <row r="42">
@@ -5255,10 +5255,10 @@
         <v>46</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0418308381622156</v>
+        <v>0.0418724329699855</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00227483120162912</v>
+        <v>0.00227996851973016</v>
       </c>
     </row>
     <row r="43">
@@ -5269,10 +5269,10 @@
         <v>36</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0395115446403002</v>
+        <v>0.0395066125521917</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0247330327024546</v>
+        <v>0.0247243278697862</v>
       </c>
     </row>
     <row r="44">
@@ -5283,7 +5283,7 @@
         <v>52</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0392691839164841</v>
+        <v>0.0392511350081696</v>
       </c>
       <c r="D44"/>
     </row>
@@ -5295,10 +5295,10 @@
         <v>58</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0381616940136496</v>
+        <v>0.038163478837976</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00332034303528012</v>
+        <v>0.00333168206607531</v>
       </c>
     </row>
     <row r="46">
@@ -5309,7 +5309,7 @@
         <v>43</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0249361679200066</v>
+        <v>0.0249759713274991</v>
       </c>
       <c r="D46"/>
     </row>
@@ -5321,10 +5321,10 @@
         <v>45</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0181355363891992</v>
+        <v>0.018164531032724</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00320584844785667</v>
+        <v>0.00321106576757816</v>
       </c>
     </row>
     <row r="48">
@@ -5335,10 +5335,10 @@
         <v>30</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0181352769023429</v>
+        <v>0.018164531032724</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00392649625977749</v>
+        <v>0.00393273633054245</v>
       </c>
     </row>
     <row r="49">
@@ -5349,10 +5349,10 @@
         <v>59</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0166240254510523</v>
+        <v>0.0166508201133304</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00320603193277241</v>
+        <v>0.00321106576757816</v>
       </c>
     </row>
     <row r="50">
@@ -5363,7 +5363,7 @@
         <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00950007329725242</v>
+        <v>0.00949822540819951</v>
       </c>
       <c r="D50"/>
     </row>
@@ -5375,10 +5375,10 @@
         <v>60</v>
       </c>
       <c r="C51" t="n">
-        <v>0.00755625725645272</v>
+        <v>0.00756855459696835</v>
       </c>
       <c r="D51" t="n">
-        <v>0.000436260716107904</v>
+        <v>0.000436970703393606</v>
       </c>
     </row>
     <row r="52">
@@ -5389,7 +5389,7 @@
         <v>61</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00572194466902606</v>
+        <v>0.00571394810971534</v>
       </c>
       <c r="D52"/>
     </row>
@@ -5401,7 +5401,7 @@
         <v>47</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00377812862822636</v>
+        <v>0.00378427729848418</v>
       </c>
       <c r="D53"/>
     </row>
@@ -5413,7 +5413,7 @@
         <v>62</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00377812862822636</v>
+        <v>0.00378427729848418</v>
       </c>
       <c r="D54"/>
     </row>
@@ -5425,7 +5425,7 @@
         <v>63</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00377812862822636</v>
+        <v>0.00378427729848418</v>
       </c>
       <c r="D55"/>
     </row>
@@ -5437,7 +5437,7 @@
         <v>49</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00226687717693582</v>
+        <v>0.00227056637909051</v>
       </c>
       <c r="D56"/>
     </row>
@@ -5449,7 +5449,7 @@
         <v>64</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00151125145129054</v>
+        <v>0.00151371091939367</v>
       </c>
       <c r="D57"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>20.8964303849511</v>
+        <v>20.9089447913448</v>
       </c>
       <c r="D2" t="n">
-        <v>0.40132129824461</v>
+        <v>0.401548463398476</v>
       </c>
     </row>
     <row r="3">
@@ -5500,10 +5500,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>19.5042676185709</v>
+        <v>19.515544868518</v>
       </c>
       <c r="D3" t="n">
-        <v>0.69661792465398</v>
+        <v>0.696985593092147</v>
       </c>
     </row>
     <row r="4">
@@ -5514,10 +5514,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>16.386303133668</v>
+        <v>16.3958607679291</v>
       </c>
       <c r="D4" t="n">
-        <v>0.290895009281827</v>
+        <v>0.291073913008381</v>
       </c>
     </row>
     <row r="5">
@@ -5528,10 +5528,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>9.17085236769273</v>
+        <v>9.1755397894374</v>
       </c>
       <c r="D5" t="n">
-        <v>0.154400412377886</v>
+        <v>0.154467878368674</v>
       </c>
     </row>
     <row r="6">
@@ -5542,10 +5542,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>5.71454646362709</v>
+        <v>5.71789742115047</v>
       </c>
       <c r="D6" t="n">
-        <v>0.206228511263732</v>
+        <v>0.206357654023963</v>
       </c>
     </row>
     <row r="7">
@@ -5556,10 +5556,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="n">
-        <v>4.95123189842388</v>
+        <v>4.9528368368046</v>
       </c>
       <c r="D7" t="n">
-        <v>0.275070137301916</v>
+        <v>0.275160029564291</v>
       </c>
     </row>
     <row r="8">
@@ -5570,10 +5570,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>4.52032294518168</v>
+        <v>4.52291121929776</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0997315548983837</v>
+        <v>0.0997945309150426</v>
       </c>
     </row>
     <row r="9">
@@ -5584,10 +5584,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>3.17853709867649</v>
+        <v>3.18047784399733</v>
       </c>
       <c r="D9" t="n">
-        <v>0.250871421747966</v>
+        <v>0.251027157324448</v>
       </c>
     </row>
     <row r="10">
@@ -5598,10 +5598,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>2.99700233767411</v>
+        <v>2.99870189874216</v>
       </c>
       <c r="D10" t="n">
-        <v>0.412461935476599</v>
+        <v>0.412733221848607</v>
       </c>
     </row>
     <row r="11">
@@ -5612,10 +5612,10 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>2.69657448223904</v>
+        <v>2.69829418638826</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0960038258063685</v>
+        <v>0.0960589851709551</v>
       </c>
     </row>
     <row r="12">
@@ -5626,10 +5626,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>1.85877932897663</v>
+        <v>1.85990747624576</v>
       </c>
       <c r="D12" t="n">
-        <v>0.236255745030162</v>
+        <v>0.236417664315277</v>
       </c>
     </row>
     <row r="13">
@@ -5640,10 +5640,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>1.78999711583112</v>
+        <v>1.7910378172363</v>
       </c>
       <c r="D13" t="n">
-        <v>0.201818015072672</v>
+        <v>0.201941963215388</v>
       </c>
     </row>
     <row r="14">
@@ -5654,10 +5654,10 @@
         <v>56</v>
       </c>
       <c r="C14" t="n">
-        <v>0.78444889947151</v>
+        <v>0.784900525992636</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000796682749617929</v>
+        <v>0.00074271630276275</v>
       </c>
     </row>
     <row r="15">
@@ -5668,10 +5668,10 @@
         <v>66</v>
       </c>
       <c r="C15" t="n">
-        <v>0.496690365542085</v>
+        <v>0.496846185347191</v>
       </c>
       <c r="D15" t="n">
-        <v>0.103490352577644</v>
+        <v>0.103501694980718</v>
       </c>
     </row>
     <row r="16">
@@ -5682,10 +5682,10 @@
         <v>44</v>
       </c>
       <c r="C16" t="n">
-        <v>0.471706031986484</v>
+        <v>0.471948170244991</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0338485349569207</v>
+        <v>0.0338694458982065</v>
       </c>
     </row>
     <row r="17">
@@ -5696,10 +5696,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>0.397476362042375</v>
+        <v>0.39759252868929</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0395989181271842</v>
+        <v>0.0396581606208257</v>
       </c>
     </row>
     <row r="18">
@@ -5710,10 +5710,10 @@
         <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>0.362564825144564</v>
+        <v>0.362756151255506</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0636974772552447</v>
+        <v>0.0637259770151603</v>
       </c>
     </row>
     <row r="19">
@@ -5724,10 +5724,10 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>0.352257975338295</v>
+        <v>0.352373940526006</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0130045760989202</v>
+        <v>0.0130086994782773</v>
       </c>
     </row>
     <row r="20">
@@ -5738,10 +5738,10 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>0.326956520516699</v>
+        <v>0.327118312764345</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0902193276254259</v>
+        <v>0.0902631108791568</v>
       </c>
     </row>
     <row r="21">
@@ -5752,10 +5752,10 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>0.30053124677566</v>
+        <v>0.300706063486938</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1576618403062</v>
+        <v>0.157754624402882</v>
       </c>
     </row>
     <row r="22">
@@ -5766,7 +5766,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.271530997394112</v>
+        <v>0.271703881154662</v>
       </c>
       <c r="D22"/>
     </row>
@@ -5778,10 +5778,10 @@
         <v>59</v>
       </c>
       <c r="C23" t="n">
-        <v>0.207724645762468</v>
+        <v>0.207840390677484</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0273548802493659</v>
+        <v>0.0273669405471404</v>
       </c>
     </row>
     <row r="24">
@@ -5789,13 +5789,13 @@
         <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C24" t="n">
-        <v>0.204513384282842</v>
+        <v>0.19101052587293</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0300462463677625</v>
+        <v>0.00635264424884057</v>
       </c>
     </row>
     <row r="25">
@@ -5803,24 +5803,22 @@
         <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>0.190912723389046</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0063497165896928</v>
-      </c>
+        <v>0.186103262784747</v>
+      </c>
+      <c r="D25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
         <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>0.185969963450629</v>
+        <v>0.184101040591942</v>
       </c>
       <c r="D26"/>
     </row>
@@ -5829,10 +5827,10 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C27" t="n">
-        <v>0.183979782309654</v>
+        <v>0.159831606370032</v>
       </c>
       <c r="D27"/>
     </row>
@@ -5841,25 +5839,27 @@
         <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C28" t="n">
-        <v>0.159746568453665</v>
-      </c>
-      <c r="D28"/>
+        <v>0.155570498269974</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0425816934424559</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
         <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>0.155486273095418</v>
+        <v>0.148156268263917</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0425551221000563</v>
+        <v>0.0324774657870456</v>
       </c>
     </row>
     <row r="30">
@@ -5870,10 +5870,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.135660472710767</v>
+        <v>0.135768974440336</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0159734005653378</v>
+        <v>0.0159864296122938</v>
       </c>
     </row>
     <row r="31">
@@ -5884,10 +5884,10 @@
         <v>26</v>
       </c>
       <c r="C31" t="n">
-        <v>0.132151297052132</v>
+        <v>0.132244344068678</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0430081157464143</v>
+        <v>0.0430420528215539</v>
       </c>
     </row>
     <row r="32">
@@ -5898,10 +5898,10 @@
         <v>13</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0932083151942146</v>
+        <v>0.0932543466827657</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0194173692160504</v>
+        <v>0.0194212023130447</v>
       </c>
     </row>
     <row r="33">
@@ -5912,7 +5912,7 @@
         <v>50</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0898818111926673</v>
+        <v>0.0899279358994959</v>
       </c>
       <c r="D33"/>
     </row>
@@ -5924,10 +5924,10 @@
         <v>11</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0846963063676509</v>
+        <v>0.0847562437934022</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0288236273031782</v>
+        <v>0.0288400190742536</v>
       </c>
     </row>
     <row r="35">
@@ -5938,7 +5938,7 @@
         <v>52</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0834740000447236</v>
+        <v>0.0835399520510492</v>
       </c>
       <c r="D35"/>
     </row>
@@ -5950,10 +5950,10 @@
         <v>33</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0831164212976286</v>
+        <v>0.0831680348852087</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00647232502580888</v>
+        <v>0.00647607501318592</v>
       </c>
     </row>
     <row r="37">
@@ -5964,10 +5964,10 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0763506227411646</v>
+        <v>0.0764077251707393</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0120552969894285</v>
+        <v>0.0120624116826618</v>
       </c>
     </row>
     <row r="38">
@@ -5978,10 +5978,10 @@
         <v>21</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0747098471187798</v>
+        <v>0.0747524894326581</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00570942999724961</v>
+        <v>0.00571244638256003</v>
       </c>
     </row>
     <row r="39">
@@ -5992,10 +5992,10 @@
         <v>55</v>
       </c>
       <c r="C39" t="n">
-        <v>0.047271501704543</v>
+        <v>0.0472890632865242</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0215373081953304</v>
+        <v>0.0215376168014375</v>
       </c>
     </row>
     <row r="40">
@@ -6006,10 +6006,10 @@
         <v>31</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0453516103287114</v>
+        <v>0.0453775725341771</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00572252186786509</v>
+        <v>0.00572514801410907</v>
       </c>
     </row>
     <row r="41">
@@ -6020,10 +6020,10 @@
         <v>67</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0438322071496263</v>
+        <v>0.0438555730555069</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00806976445616811</v>
+        <v>0.00807170512260014</v>
       </c>
     </row>
     <row r="42">
@@ -6034,10 +6034,10 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0413267039514093</v>
+        <v>0.0413563714410954</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00734583684368451</v>
+        <v>0.00734913446663654</v>
       </c>
     </row>
     <row r="43">
@@ -6048,10 +6048,10 @@
         <v>35</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0386990109870421</v>
+        <v>0.0387251596678197</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0046907903090843</v>
+        <v>0.00469464611789912</v>
       </c>
     </row>
     <row r="44">
@@ -6062,10 +6062,10 @@
         <v>58</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0336794227006778</v>
+        <v>0.0337022344280622</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00251863868178097</v>
+        <v>0.00252176749334921</v>
       </c>
     </row>
     <row r="45">
@@ -6076,10 +6076,10 @@
         <v>68</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0291228478091235</v>
+        <v>0.0291350098915048</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00804947213397095</v>
+        <v>0.00805688241428863</v>
       </c>
     </row>
     <row r="46">
@@ -6090,7 +6090,7 @@
         <v>63</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0284853359857311</v>
+        <v>0.0285060203110339</v>
       </c>
       <c r="D46"/>
     </row>
@@ -6102,7 +6102,7 @@
         <v>39</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0276647438438261</v>
+        <v>0.0276784024419933</v>
       </c>
       <c r="D47"/>
     </row>
@@ -6114,7 +6114,7 @@
         <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>0.022417939805022</v>
+        <v>0.0224405009063764</v>
       </c>
       <c r="D48"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>30</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0177391751473175</v>
+        <v>0.0177408575107725</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00313587275983102</v>
+        <v>0.00313617016248288</v>
       </c>
     </row>
     <row r="50">
@@ -6140,10 +6140,10 @@
         <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0158184664486354</v>
+        <v>0.0158289580582432</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00350151235716759</v>
+        <v>0.00350213283119689</v>
       </c>
     </row>
     <row r="51">
@@ -6154,10 +6154,10 @@
         <v>60</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0119071679475532</v>
+        <v>0.0119156538132734</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0036391506505092</v>
+        <v>0.00364020367295189</v>
       </c>
     </row>
     <row r="52">
@@ -6168,7 +6168,7 @@
         <v>57</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00934077419697373</v>
+        <v>0.00935024276933867</v>
       </c>
       <c r="D52"/>
     </row>
@@ -6180,7 +6180,7 @@
         <v>69</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00834568362648631</v>
+        <v>0.00834892732284511</v>
       </c>
       <c r="D53"/>
     </row>
@@ -6192,7 +6192,7 @@
         <v>62</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00560438278589919</v>
+        <v>0.00561022740163965</v>
       </c>
       <c r="D54"/>
     </row>
@@ -6204,7 +6204,7 @@
         <v>22</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00280219139294959</v>
+        <v>0.00280490935072871</v>
       </c>
       <c r="D55"/>
     </row>
@@ -6664,10 +6664,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>39.0894140297687</v>
+        <v>39.0952966098138</v>
       </c>
       <c r="D2" t="n">
-        <v>3.59628765007145</v>
+        <v>3.59635502935146</v>
       </c>
     </row>
     <row r="3">
@@ -6678,10 +6678,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>26.0292041624546</v>
+        <v>26.0206176802989</v>
       </c>
       <c r="D3" t="n">
-        <v>0.700672635988902</v>
+        <v>0.70355565817928</v>
       </c>
     </row>
     <row r="4">
@@ -6692,10 +6692,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>8.39705483155794</v>
+        <v>8.40128249364468</v>
       </c>
       <c r="D4" t="n">
-        <v>1.45049160456604</v>
+        <v>1.45112330583141</v>
       </c>
     </row>
     <row r="5">
@@ -6706,10 +6706,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>6.48240085272808</v>
+        <v>6.48379957365363</v>
       </c>
       <c r="D5" t="n">
-        <v>0.234655543131993</v>
+        <v>0.234833452484833</v>
       </c>
     </row>
     <row r="6">
@@ -6720,10 +6720,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>3.95441726432908</v>
+        <v>3.95174920905854</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0592995521701008</v>
+        <v>0.0593032181861534</v>
       </c>
     </row>
     <row r="7">
@@ -6734,10 +6734,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>3.78010700255298</v>
+        <v>3.78073413732646</v>
       </c>
       <c r="D7" t="n">
-        <v>0.694146325060293</v>
+        <v>0.694330503232789</v>
       </c>
     </row>
     <row r="8">
@@ -6748,10 +6748,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3537030739917</v>
+        <v>3.35455144158946</v>
       </c>
       <c r="D8" t="n">
-        <v>0.144563414621337</v>
+        <v>0.144672399911648</v>
       </c>
     </row>
     <row r="9">
@@ -6762,10 +6762,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>2.23249194006598</v>
+        <v>2.23270834135487</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0848863923607526</v>
+        <v>0.0849080295147432</v>
       </c>
     </row>
     <row r="10">
@@ -6776,10 +6776,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>1.69904333505729</v>
+        <v>1.69818423718239</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0980047599464985</v>
+        <v>0.0979776536173382</v>
       </c>
     </row>
     <row r="11">
@@ -6790,10 +6790,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0004487453954</v>
+        <v>0.999996488870401</v>
       </c>
       <c r="D11" t="n">
-        <v>0.202362964067628</v>
+        <v>0.202308915063461</v>
       </c>
     </row>
     <row r="12">
@@ -6804,10 +6804,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>0.74934106595931</v>
+        <v>0.749610919232174</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0613549060668165</v>
+        <v>0.0613921924698202</v>
       </c>
     </row>
     <row r="13">
@@ -6818,10 +6818,10 @@
         <v>46</v>
       </c>
       <c r="C13" t="n">
-        <v>0.562946587965616</v>
+        <v>0.56199199831418</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0217281043945719</v>
+        <v>0.0217094814929084</v>
       </c>
     </row>
     <row r="14">
@@ -6832,10 +6832,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.478921454346623</v>
+        <v>0.478902827346033</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0895865324563959</v>
+        <v>0.0895618084225907</v>
       </c>
     </row>
     <row r="15">
@@ -6846,10 +6846,10 @@
         <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>0.464598357214605</v>
+        <v>0.464524677260239</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0264376006717907</v>
+        <v>0.0264396397731457</v>
       </c>
     </row>
     <row r="16">
@@ -6860,10 +6860,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.395270213094792</v>
+        <v>0.395516103022254</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0274649751318912</v>
+        <v>0.0274847777815742</v>
       </c>
     </row>
     <row r="17">
@@ -6874,10 +6874,10 @@
         <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>0.223119431361525</v>
+        <v>0.222999502669321</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0286728746585574</v>
+        <v>0.0286279496227494</v>
       </c>
     </row>
     <row r="18">
@@ -6888,10 +6888,10 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.191007556800886</v>
+        <v>0.190919531515333</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0850673819655467</v>
+        <v>0.0850350041895554</v>
       </c>
     </row>
     <row r="19">
@@ -6902,10 +6902,10 @@
         <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>0.174168980413035</v>
+        <v>0.174169509243465</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0354548605205722</v>
+        <v>0.0354207485863615</v>
       </c>
     </row>
     <row r="20">
@@ -6916,7 +6916,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.128692038016093</v>
+        <v>0.128673973109151</v>
       </c>
       <c r="D20"/>
     </row>
@@ -6928,10 +6928,10 @@
         <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0993811876297766</v>
+        <v>0.0993776135970931</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00851454564575463</v>
+        <v>0.00851984740387219</v>
       </c>
     </row>
     <row r="22">
@@ -6942,10 +6942,10 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0984969675949759</v>
+        <v>0.0985206599328752</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0131444517864606</v>
+        <v>0.0131484823189983</v>
       </c>
     </row>
     <row r="23">
@@ -6956,10 +6956,10 @@
         <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0916837763740432</v>
+        <v>0.091624488974428</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00464564087681643</v>
+        <v>0.00465218924057146</v>
       </c>
     </row>
     <row r="24">
@@ -6970,10 +6970,10 @@
         <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0768018909485317</v>
+        <v>0.0768595195263139</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0174462015540202</v>
+        <v>0.0174770476255849</v>
       </c>
     </row>
     <row r="25">
@@ -6984,7 +6984,7 @@
         <v>40</v>
       </c>
       <c r="C25" t="n">
-        <v>0.050014720847038</v>
+        <v>0.049946562392862</v>
       </c>
       <c r="D25"/>
     </row>
@@ -6996,7 +6996,7 @@
         <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>0.044608751646077</v>
+        <v>0.0446616428551576</v>
       </c>
       <c r="D26"/>
     </row>
@@ -7008,10 +7008,10 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>0.032299379905287</v>
+        <v>0.0323507447076118</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0134347088957217</v>
+        <v>0.0134562596242251</v>
       </c>
     </row>
     <row r="28">
@@ -7022,7 +7022,7 @@
         <v>52</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0284996940643412</v>
+        <v>0.0285450372890889</v>
       </c>
       <c r="D28"/>
     </row>
@@ -7034,10 +7034,10 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0265992919828008</v>
+        <v>0.026642555521522</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00431860549041814</v>
+        <v>0.00432559864222446</v>
       </c>
     </row>
     <row r="30">
@@ -7048,10 +7048,10 @@
         <v>44</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0132506262044795</v>
+        <v>0.0132504228679513</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00137805403599971</v>
+        <v>0.00139575423785792</v>
       </c>
     </row>
     <row r="31">
@@ -7062,10 +7062,10 @@
         <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0132181948625623</v>
+        <v>0.0132031862727449</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00397258079123023</v>
+        <v>0.00395345349603923</v>
       </c>
     </row>
     <row r="32">
@@ -7076,7 +7076,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00949977376343207</v>
+        <v>0.0095150124296963</v>
       </c>
       <c r="D32"/>
     </row>
@@ -7088,10 +7088,10 @@
         <v>35</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00850931312579908</v>
+        <v>0.00850481878732842</v>
       </c>
       <c r="D33" t="n">
-        <v>0.000642898583359467</v>
+        <v>0.000631205986594875</v>
       </c>
     </row>
     <row r="34">
@@ -7102,7 +7102,7 @@
         <v>53</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0066171120732492</v>
+        <v>0.00661349527059768</v>
       </c>
       <c r="D34"/>
     </row>
@@ -7114,7 +7114,7 @@
         <v>41</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00659288176032254</v>
+        <v>0.00657816080961648</v>
       </c>
       <c r="D35"/>
     </row>
@@ -7126,7 +7126,7 @@
         <v>69</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00474988688171603</v>
+        <v>0.00475750621484815</v>
       </c>
       <c r="D36"/>
     </row>
@@ -7138,7 +7138,7 @@
         <v>33</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00282562726129395</v>
+        <v>0.0028193180446055</v>
       </c>
       <c r="D37"/>
     </row>
@@ -7175,10 +7175,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>41.1718079418187</v>
+        <v>39.9462375160072</v>
       </c>
       <c r="D2" t="n">
-        <v>5.93339273499029</v>
+        <v>5.75677204849138</v>
       </c>
     </row>
     <row r="3">
@@ -7189,10 +7189,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>29.5074444067276</v>
+        <v>30.4898559224375</v>
       </c>
       <c r="D3" t="n">
-        <v>3.10190035323069</v>
+        <v>3.21937678919411</v>
       </c>
     </row>
     <row r="4">
@@ -7203,10 +7203,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>10.060081755239</v>
+        <v>10.3359218722062</v>
       </c>
       <c r="D4" t="n">
-        <v>1.47369612469816</v>
+        <v>1.53178179146793</v>
       </c>
     </row>
     <row r="5">
@@ -7217,10 +7217,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>5.57889481709595</v>
+        <v>5.8017006809915</v>
       </c>
       <c r="D5" t="n">
-        <v>0.701194457608871</v>
+        <v>0.731220483136467</v>
       </c>
     </row>
     <row r="6">
@@ -7231,10 +7231,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>2.85264067893009</v>
+        <v>2.76772589483193</v>
       </c>
       <c r="D6" t="n">
-        <v>0.469476589410057</v>
+        <v>0.455501589693251</v>
       </c>
     </row>
     <row r="7">
@@ -7245,10 +7245,10 @@
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>1.92099111770672</v>
+        <v>1.86380829784369</v>
       </c>
       <c r="D7" t="n">
-        <v>1.08148531041222</v>
+        <v>1.04929251082191</v>
       </c>
     </row>
     <row r="8">
@@ -7256,13 +7256,13 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1.77062585437902</v>
+        <v>1.78027450076551</v>
       </c>
       <c r="D8" t="n">
-        <v>0.330967844097034</v>
+        <v>0.706282699269884</v>
       </c>
     </row>
     <row r="9">
@@ -7273,10 +7273,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>1.74120697283712</v>
+        <v>1.73668423394499</v>
       </c>
       <c r="D9" t="n">
-        <v>0.421277831112661</v>
+        <v>0.417080186074943</v>
       </c>
     </row>
     <row r="10">
@@ -7284,13 +7284,13 @@
         <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>1.72873014407748</v>
+        <v>1.71791922717238</v>
       </c>
       <c r="D10" t="n">
-        <v>0.675283659480606</v>
+        <v>0.321115827906639</v>
       </c>
     </row>
     <row r="11">
@@ -7301,10 +7301,10 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>1.50845605156561</v>
+        <v>1.47335905216695</v>
       </c>
       <c r="D11" t="n">
-        <v>0.361203952932458</v>
+        <v>0.353837918265473</v>
       </c>
     </row>
     <row r="12">
@@ -7315,10 +7315,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.460301397706656</v>
+        <v>0.446599394073284</v>
       </c>
       <c r="D12" t="n">
-        <v>0.137756348833275</v>
+        <v>0.133655673939</v>
       </c>
     </row>
     <row r="13">
@@ -7329,10 +7329,10 @@
         <v>44</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4099749483374</v>
+        <v>0.397771274371681</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0841914301208261</v>
+        <v>0.0816852675048394</v>
       </c>
     </row>
     <row r="14">
@@ -7343,7 +7343,7 @@
         <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>0.253472674096982</v>
+        <v>0.245927415660807</v>
       </c>
       <c r="D14"/>
     </row>
@@ -7355,7 +7355,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>0.216034696751123</v>
+        <v>0.209603970101352</v>
       </c>
       <c r="D15"/>
     </row>
@@ -7367,10 +7367,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>0.204373846161008</v>
+        <v>0.198290253567116</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0785496251358165</v>
+        <v>0.076211529812794</v>
       </c>
     </row>
     <row r="17">
@@ -7381,7 +7381,7 @@
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>0.175528305303381</v>
+        <v>0.170303320892579</v>
       </c>
       <c r="D17"/>
     </row>
@@ -7393,10 +7393,10 @@
         <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>0.160184955831317</v>
+        <v>0.155416731534608</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0871698646697973</v>
+        <v>0.0845749904325371</v>
       </c>
     </row>
     <row r="19">
@@ -7407,7 +7407,7 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>0.132566853698023</v>
+        <v>0.128620566097522</v>
       </c>
       <c r="D19"/>
     </row>
@@ -7416,24 +7416,22 @@
         <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0570773623530884</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.028208508146099</v>
-      </c>
+        <v>0.0500190773095149</v>
+      </c>
+      <c r="D20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
         <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0515537053846396</v>
+        <v>0.0470418736601977</v>
       </c>
       <c r="D21"/>
     </row>
@@ -7445,7 +7443,7 @@
         <v>46</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0380515139990757</v>
+        <v>0.0369189243634112</v>
       </c>
       <c r="D22"/>
     </row>
@@ -7482,10 +7480,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>66.9149631570192</v>
+        <v>70.5302784358677</v>
       </c>
       <c r="D2" t="n">
-        <v>21.4000508821251</v>
+        <v>22.5567907385203</v>
       </c>
     </row>
     <row r="3">
@@ -7496,10 +7494,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>11.79447177723</v>
+        <v>12.3921880590485</v>
       </c>
       <c r="D3" t="n">
-        <v>0.638867191005388</v>
+        <v>0.671645089235907</v>
       </c>
     </row>
     <row r="4">
@@ -7507,13 +7505,13 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>5.16204770343371</v>
+        <v>4.14652991863971</v>
       </c>
       <c r="D4" t="n">
-        <v>1.89363926668152</v>
+        <v>0.318607197439437</v>
       </c>
     </row>
     <row r="5">
@@ -7521,13 +7519,13 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>3.94179647314797</v>
+        <v>2.21896262787719</v>
       </c>
       <c r="D5" t="n">
-        <v>0.302597454629166</v>
+        <v>0.126907583328157</v>
       </c>
     </row>
     <row r="6">
@@ -7535,13 +7533,13 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.10886279438119</v>
+        <v>1.96138700948456</v>
       </c>
       <c r="D6" t="n">
-        <v>0.120332182319939</v>
+        <v>0.10391715640584</v>
       </c>
     </row>
     <row r="7">
@@ -7549,13 +7547,13 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>1.86564102404566</v>
+        <v>1.55069117837761</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0974475496521175</v>
+        <v>0.181092844480868</v>
       </c>
     </row>
     <row r="8">
@@ -7563,13 +7561,13 @@
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4709532566092</v>
+        <v>1.47978615723959</v>
       </c>
       <c r="D8" t="n">
-        <v>0.171645206705724</v>
+        <v>0.183344623430711</v>
       </c>
     </row>
     <row r="9">
@@ -7577,13 +7575,13 @@
         <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.40718984495831</v>
+        <v>1.24597499043737</v>
       </c>
       <c r="D9" t="n">
-        <v>0.174328049148535</v>
+        <v>0.0225704004201486</v>
       </c>
     </row>
     <row r="10">
@@ -7591,13 +7589,13 @@
         <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>1.18921817514619</v>
+        <v>0.715483269502467</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0215434445268177</v>
+        <v>0.0311252723179224</v>
       </c>
     </row>
     <row r="11">
@@ -7605,13 +7603,13 @@
         <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>0.680942861454395</v>
+        <v>0.649903753598018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0295863233606748</v>
+        <v>0.0325187552380129</v>
       </c>
     </row>
     <row r="12">
@@ -7619,13 +7617,13 @@
         <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="C12" t="n">
-        <v>0.618186057437879</v>
+        <v>0.436806884733782</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0308465659471544</v>
+        <v>0.0457184107935417</v>
       </c>
     </row>
     <row r="13">
@@ -7633,13 +7631,13 @@
         <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>0.414669544395508</v>
+        <v>0.415678513469296</v>
       </c>
       <c r="D13" t="n">
-        <v>0.043280885578752</v>
+        <v>0.0417576852249246</v>
       </c>
     </row>
     <row r="14">
@@ -7647,13 +7645,13 @@
         <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>0.396367052261907</v>
+        <v>0.345967030717012</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0398533728099358</v>
+        <v>0.0236725170325631</v>
       </c>
     </row>
     <row r="15">
@@ -7661,13 +7659,13 @@
         <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>0.329912039938482</v>
+        <v>0.335021692452911</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0225425203494648</v>
+        <v>0.127228933141411</v>
       </c>
     </row>
     <row r="16">
@@ -7675,13 +7673,13 @@
         <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>0.319862731469542</v>
+        <v>0.230648728400865</v>
       </c>
       <c r="D16" t="n">
-        <v>0.121472031497207</v>
+        <v>0.109912767110122</v>
       </c>
     </row>
     <row r="17">
@@ -7689,13 +7687,13 @@
         <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>0.218825761138256</v>
+        <v>0.207308981749391</v>
       </c>
       <c r="D17" t="n">
-        <v>0.104140478572011</v>
+        <v>0.052280369474295</v>
       </c>
     </row>
     <row r="18">
@@ -7703,13 +7701,13 @@
         <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.197137763725047</v>
+        <v>0.185653133292395</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0495911782550461</v>
+        <v>0.03602482271634</v>
       </c>
     </row>
     <row r="19">
@@ -7717,13 +7715,13 @@
         <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C19" t="n">
-        <v>0.176400362109036</v>
+        <v>0.160286852094733</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0341670479394432</v>
+        <v>0.00933436776488099</v>
       </c>
     </row>
     <row r="20">
@@ -7731,13 +7729,13 @@
         <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>0.153034150160258</v>
+        <v>0.120509700017397</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00891198989870323</v>
+        <v>0.019972460926088</v>
       </c>
     </row>
     <row r="21">
@@ -7748,10 +7746,10 @@
         <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>0.104433535273012</v>
+        <v>0.10983500157166</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0296460509004225</v>
+        <v>0.031243726071773</v>
       </c>
     </row>
     <row r="22">
@@ -7762,10 +7760,10 @@
         <v>14</v>
       </c>
       <c r="C22" t="n">
-        <v>0.101735334479538</v>
+        <v>0.1065567345506</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0247737525905765</v>
+        <v>0.0259478012828408</v>
       </c>
     </row>
     <row r="23">
@@ -7776,10 +7774,10 @@
         <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>0.100032503276675</v>
+        <v>0.105149817838046</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0000151361846732927</v>
+        <v>0.000282111030677098</v>
       </c>
     </row>
     <row r="24">
@@ -7790,10 +7788,10 @@
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0862163095667071</v>
+        <v>0.0903019317313388</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00513534747416548</v>
+        <v>0.00537874046327986</v>
       </c>
     </row>
     <row r="25">
@@ -7804,10 +7802,10 @@
         <v>27</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0564718834455461</v>
+        <v>0.0591477634188317</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0114453772041422</v>
+        <v>0.0119877716264272</v>
       </c>
     </row>
     <row r="26">
@@ -7818,10 +7816,10 @@
         <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0331932568854764</v>
+        <v>0.0347663052680059</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00766715689684907</v>
+        <v>0.00803048605511114</v>
       </c>
     </row>
     <row r="27">
@@ -7832,10 +7830,10 @@
         <v>31</v>
       </c>
       <c r="C27" t="n">
-        <v>0.029313634443504</v>
+        <v>0.030702791082707</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000609609837716902</v>
+        <v>0.000638475689344483</v>
       </c>
     </row>
     <row r="28">
@@ -7846,10 +7844,10 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0264998423427328</v>
+        <v>0.0278740360962826</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0059357809545044</v>
+        <v>0.00630074346355175</v>
       </c>
     </row>
     <row r="29">
@@ -7857,10 +7855,10 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>0.021554032796265</v>
+        <v>0.0226175430837933</v>
       </c>
       <c r="D29"/>
     </row>
@@ -7869,10 +7867,10 @@
         <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0214400469237918</v>
+        <v>0.0225755761925929</v>
       </c>
       <c r="D30"/>
     </row>
@@ -7884,7 +7882,7 @@
         <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0137946095306731</v>
+        <v>0.0144483613024788</v>
       </c>
       <c r="D31"/>
     </row>
@@ -7896,7 +7894,7 @@
         <v>42</v>
       </c>
       <c r="C32" t="n">
-        <v>0.010777105588956</v>
+        <v>0.0112877880962965</v>
       </c>
       <c r="D32"/>
     </row>
@@ -7908,7 +7906,7 @@
         <v>41</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00991480870705368</v>
+        <v>0.01038484711718</v>
       </c>
       <c r="D33"/>
     </row>
@@ -7920,10 +7918,10 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00689730476533657</v>
+        <v>0.00722408739148118</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00121921967543381</v>
+        <v>0.00127708326790387</v>
       </c>
     </row>
     <row r="35">
@@ -7934,7 +7932,7 @@
         <v>40</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00560403782413008</v>
+        <v>0.00586958266304824</v>
       </c>
       <c r="D35"/>
     </row>
@@ -7946,10 +7944,10 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00517306776482596</v>
+        <v>0.00541820543324822</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00121921967543381</v>
+        <v>0.00127708326790387</v>
       </c>
     </row>
     <row r="37">
@@ -7960,7 +7958,7 @@
         <v>53</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00344865238266829</v>
+        <v>0.00361213695549881</v>
       </c>
       <c r="D37"/>
     </row>
@@ -7972,7 +7970,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0030175039417171</v>
+        <v>0.00316057320618235</v>
       </c>
       <c r="D38"/>
     </row>
@@ -8009,10 +8007,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>29.7405431114286</v>
+        <v>29.7418505567455</v>
       </c>
       <c r="D2" t="n">
-        <v>0.679793153831704</v>
+        <v>0.67994647005535</v>
       </c>
     </row>
     <row r="3">
@@ -8023,10 +8021,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>15.91808389177</v>
+        <v>15.917029579138</v>
       </c>
       <c r="D3" t="n">
-        <v>0.24487522103406</v>
+        <v>0.246139394840846</v>
       </c>
     </row>
     <row r="4">
@@ -8037,10 +8035,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>8.94724079789297</v>
+        <v>8.94540740014866</v>
       </c>
       <c r="D4" t="n">
-        <v>0.242258634432867</v>
+        <v>0.242210509512302</v>
       </c>
     </row>
     <row r="5">
@@ -8051,10 +8049,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>7.48092123887055</v>
+        <v>7.48067612654042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.204461373294285</v>
+        <v>0.204455727034424</v>
       </c>
     </row>
     <row r="6">
@@ -8065,10 +8063,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>5.8879932207304</v>
+        <v>5.8901770117495</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7940033267511</v>
+        <v>1.79469323944126</v>
       </c>
     </row>
     <row r="7">
@@ -8079,10 +8077,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.94495019392502</v>
+        <v>4.94511192434148</v>
       </c>
       <c r="D7" t="n">
-        <v>0.180547023141692</v>
+        <v>0.18054641125247</v>
       </c>
     </row>
     <row r="8">
@@ -8093,10 +8091,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.71753300314093</v>
+        <v>4.7178264886085</v>
       </c>
       <c r="D8" t="n">
-        <v>0.189691990744847</v>
+        <v>0.189699053849596</v>
       </c>
     </row>
     <row r="9">
@@ -8107,10 +8105,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>2.40125170239245</v>
+        <v>2.40180643368867</v>
       </c>
       <c r="D9" t="n">
-        <v>0.422835104668761</v>
+        <v>0.422934924733041</v>
       </c>
     </row>
     <row r="10">
@@ -8121,10 +8119,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>2.37372783589487</v>
+        <v>2.37401689556843</v>
       </c>
       <c r="D10" t="n">
-        <v>0.284659023971834</v>
+        <v>0.284688568181825</v>
       </c>
     </row>
     <row r="11">
@@ -8135,10 +8133,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>2.20586674630832</v>
+        <v>2.20535221829786</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0725301449778692</v>
+        <v>0.0725162922745836</v>
       </c>
     </row>
     <row r="12">
@@ -8149,10 +8147,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>2.02841741366506</v>
+        <v>2.02850234930419</v>
       </c>
       <c r="D12" t="n">
-        <v>0.225117958291179</v>
+        <v>0.225137480425796</v>
       </c>
     </row>
     <row r="13">
@@ -8163,10 +8161,10 @@
         <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>1.89028130383323</v>
+        <v>1.8898056182062</v>
       </c>
       <c r="D13" t="n">
-        <v>0.144448869484153</v>
+        <v>0.144412813565071</v>
       </c>
     </row>
     <row r="14">
@@ -8177,10 +8175,10 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>1.80167720783543</v>
+        <v>1.80135648285899</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0400686041192524</v>
+        <v>0.0400585456186932</v>
       </c>
     </row>
     <row r="15">
@@ -8191,10 +8189,10 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3921258556492</v>
+        <v>1.39210452162954</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0294285363921603</v>
+        <v>0.0294333773537676</v>
       </c>
     </row>
     <row r="16">
@@ -8205,10 +8203,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>1.35848093067553</v>
+        <v>1.35882669476989</v>
       </c>
       <c r="D16" t="n">
-        <v>0.23472338544689</v>
+        <v>0.234788804473337</v>
       </c>
     </row>
     <row r="17">
@@ -8219,10 +8217,10 @@
         <v>48</v>
       </c>
       <c r="C17" t="n">
-        <v>1.03092635440236</v>
+        <v>1.03076792351529</v>
       </c>
       <c r="D17" t="n">
-        <v>0.414039805304403</v>
+        <v>0.413947971654001</v>
       </c>
     </row>
     <row r="18">
@@ -8233,10 +8231,10 @@
         <v>40</v>
       </c>
       <c r="C18" t="n">
-        <v>0.712588525277504</v>
+        <v>0.712365291560759</v>
       </c>
       <c r="D18" t="n">
-        <v>0.259171898905453</v>
+        <v>0.259072725416868</v>
       </c>
     </row>
     <row r="19">
@@ -8247,10 +8245,10 @@
         <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>0.609773384013117</v>
+        <v>0.609826620035675</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0386924247635504</v>
+        <v>0.038698009245817</v>
       </c>
     </row>
     <row r="20">
@@ -8261,10 +8259,10 @@
         <v>38</v>
       </c>
       <c r="C20" t="n">
-        <v>0.511656339218621</v>
+        <v>0.511528401622383</v>
       </c>
       <c r="D20" t="n">
-        <v>0.081509597943261</v>
+        <v>0.0814896219892298</v>
       </c>
     </row>
     <row r="21">
@@ -8275,10 +8273,10 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>0.453347071163575</v>
+        <v>0.453459289941151</v>
       </c>
       <c r="D21" t="n">
-        <v>0.111812654845171</v>
+        <v>0.111845194777086</v>
       </c>
     </row>
     <row r="22">
@@ -8289,10 +8287,10 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.378337403563022</v>
+        <v>0.378363056668583</v>
       </c>
       <c r="D22" t="n">
-        <v>0.014661016653813</v>
+        <v>0.0146628445433006</v>
       </c>
     </row>
     <row r="23">
@@ -8303,10 +8301,10 @@
         <v>45</v>
       </c>
       <c r="C23" t="n">
-        <v>0.314983420087856</v>
+        <v>0.314855384022692</v>
       </c>
       <c r="D23" t="n">
-        <v>0.205998892753032</v>
+        <v>0.205912927227987</v>
       </c>
     </row>
     <row r="24">
@@ -8317,10 +8315,10 @@
         <v>33</v>
       </c>
       <c r="C24" t="n">
-        <v>0.296905168753593</v>
+        <v>0.296858570823821</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0354081298178362</v>
+        <v>0.03540388606653</v>
       </c>
     </row>
     <row r="25">
@@ -8331,10 +8329,10 @@
         <v>26</v>
       </c>
       <c r="C25" t="n">
-        <v>0.282864945266298</v>
+        <v>0.282930152636124</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0103614650116107</v>
+        <v>0.0103643542256096</v>
       </c>
     </row>
     <row r="26">
@@ -8345,10 +8343,10 @@
         <v>46</v>
       </c>
       <c r="C26" t="n">
-        <v>0.264932638753184</v>
+        <v>0.264933007918755</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0109945527792294</v>
+        <v>0.0109963316090334</v>
       </c>
     </row>
     <row r="27">
@@ -8359,10 +8357,10 @@
         <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>0.25445280551637</v>
+        <v>0.254413262930607</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0640791308699394</v>
+        <v>0.0640690848246998</v>
       </c>
     </row>
     <row r="28">
@@ -8373,10 +8371,10 @@
         <v>56</v>
       </c>
       <c r="C28" t="n">
-        <v>0.231076757174404</v>
+        <v>0.230988828877522</v>
       </c>
       <c r="D28" t="n">
-        <v>0.137312971803725</v>
+        <v>0.137261219679964</v>
       </c>
     </row>
     <row r="29">
@@ -8387,10 +8385,10 @@
         <v>44</v>
       </c>
       <c r="C29" t="n">
-        <v>0.22489101860712</v>
+        <v>0.224833193401034</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0235199731107208</v>
+        <v>0.0235164627515076</v>
       </c>
     </row>
     <row r="30">
@@ -8401,10 +8399,10 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>0.223432233781182</v>
+        <v>0.22338445756345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.057164364055876</v>
+        <v>0.0571533290425653</v>
       </c>
     </row>
     <row r="31">
@@ -8415,10 +8413,10 @@
         <v>20</v>
       </c>
       <c r="C31" t="n">
-        <v>0.168511539118992</v>
+        <v>0.168488972466471</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0635461701984379</v>
+        <v>0.0635341590746958</v>
       </c>
     </row>
     <row r="32">
@@ -8429,10 +8427,10 @@
         <v>18</v>
       </c>
       <c r="C32" t="n">
-        <v>0.16319516731587</v>
+        <v>0.163170752716696</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0109239065557617</v>
+        <v>0.0109204198309735</v>
       </c>
     </row>
     <row r="33">
@@ -8443,10 +8441,10 @@
         <v>28</v>
       </c>
       <c r="C33" t="n">
-        <v>0.136224232674787</v>
+        <v>0.13621465210119</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00426898068416933</v>
+        <v>0.00426823008279045</v>
       </c>
     </row>
     <row r="34">
@@ -8457,7 +8455,7 @@
         <v>41</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0850649340849339</v>
+        <v>0.0850467609991285</v>
       </c>
       <c r="D34"/>
     </row>
@@ -8469,10 +8467,10 @@
         <v>42</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0733382677056238</v>
+        <v>0.0733242668991383</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0148971898762902</v>
+        <v>0.0148973229071809</v>
       </c>
     </row>
     <row r="36">
@@ -8483,10 +8481,10 @@
         <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0723216293492119</v>
+        <v>0.0723346841817042</v>
       </c>
       <c r="D36" t="n">
-        <v>0.018069258866006</v>
+        <v>0.0180742178538264</v>
       </c>
     </row>
     <row r="37">
@@ -8497,7 +8495,7 @@
         <v>23</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0717328746729864</v>
+        <v>0.0717227010338371</v>
       </c>
       <c r="D37"/>
     </row>
@@ -8509,10 +8507,10 @@
         <v>31</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0452163591341168</v>
+        <v>0.0452274111309718</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00386049629455164</v>
+        <v>0.00386057731944866</v>
       </c>
     </row>
     <row r="39">
@@ -8523,10 +8521,10 @@
         <v>43</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0451394064102383</v>
+        <v>0.0451309392479656</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00892949104623856</v>
+        <v>0.00891401606650688</v>
       </c>
     </row>
     <row r="40">
@@ -8537,10 +8535,10 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0444995710466108</v>
+        <v>0.044506358397163</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00429281904053095</v>
+        <v>0.00429287831483393</v>
       </c>
     </row>
     <row r="41">
@@ -8551,10 +8549,10 @@
         <v>66</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0323642591680838</v>
+        <v>0.032371455285284</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00444788814586143</v>
+        <v>0.0044483233429409</v>
       </c>
     </row>
     <row r="42">
@@ -8565,10 +8563,10 @@
         <v>39</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0256600847929461</v>
+        <v>0.0256618523981318</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00244650978195188</v>
+        <v>0.00244581223328627</v>
       </c>
     </row>
     <row r="43">
@@ -8579,7 +8577,7 @@
         <v>30</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0255124815079205</v>
+        <v>0.0255086908519159</v>
       </c>
       <c r="D43"/>
     </row>
@@ -8591,10 +8589,10 @@
         <v>36</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0224161294501375</v>
+        <v>0.0224109820037737</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0070056423548661</v>
+        <v>0.00700023887334363</v>
       </c>
     </row>
     <row r="45">
@@ -8605,7 +8603,7 @@
         <v>52</v>
       </c>
       <c r="C45" t="n">
-        <v>0.022358746600004</v>
+        <v>0.0223579390440452</v>
       </c>
       <c r="D45"/>
     </row>
@@ -8617,10 +8615,10 @@
         <v>55</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0214946869202477</v>
+        <v>0.0214833932455222</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0123493510206346</v>
+        <v>0.0123428624612051</v>
       </c>
     </row>
     <row r="47">
@@ -8631,7 +8629,7 @@
         <v>59</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0194219387671587</v>
+        <v>0.0194160438901054</v>
       </c>
       <c r="D47"/>
     </row>
@@ -8643,10 +8641,10 @@
         <v>60</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0136262709036726</v>
+        <v>0.013630051539225</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00292131936281956</v>
+        <v>0.00292335824571651</v>
       </c>
     </row>
     <row r="49">
@@ -8657,7 +8655,7 @@
         <v>58</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0120331505037228</v>
+        <v>0.0120311378219102</v>
       </c>
       <c r="D49"/>
     </row>
@@ -8669,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00537375465325577</v>
+        <v>0.00537093119100512</v>
       </c>
       <c r="D50"/>
     </row>
@@ -8681,7 +8679,7 @@
         <v>67</v>
       </c>
       <c r="C51" t="n">
-        <v>0.00470207678319572</v>
+        <v>0.00469960623194177</v>
       </c>
       <c r="D51"/>
     </row>
@@ -8693,10 +8691,10 @@
         <v>63</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00433721473032359</v>
+        <v>0.00433725651329671</v>
       </c>
       <c r="D52" t="n">
-        <v>0.000217186087119586</v>
+        <v>0.000218712906696758</v>
       </c>
     </row>
     <row r="53">
@@ -8707,7 +8705,7 @@
         <v>69</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0038705229954226</v>
+        <v>0.00387213606017776</v>
       </c>
       <c r="D53"/>
     </row>
@@ -8719,7 +8717,7 @@
         <v>61</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00232218112014343</v>
+        <v>0.00232328163610665</v>
       </c>
       <c r="D54"/>
     </row>
